--- a/InitializationResults/WithTrack/Comparison of NSGAII with NSGAII_SI for each generation (on average).xlsx
+++ b/InitializationResults/WithTrack/Comparison of NSGAII with NSGAII_SI for each generation (on average).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="10995" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="10995"/>
   </bookViews>
   <sheets>
     <sheet name="EPS" sheetId="1" r:id="rId1"/>
@@ -71,10 +71,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -107,6 +107,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="it-IT"/>
+              <a:t>Epsilon</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
@@ -141,14 +166,19 @@
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+        <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>NSGAII</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -606,14 +636,19 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
+          <c:tx>
+            <c:v>NSGAII_SI</c:v>
+          </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -852,7 +887,7 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -862,11 +897,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="378599456"/>
-        <c:axId val="378606904"/>
+        <c:axId val="233025784"/>
+        <c:axId val="233030096"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="378599456"/>
+        <c:axId val="233025784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -886,6 +921,62 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="it-IT"/>
+                  <a:t>Generation</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="it-IT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -923,12 +1014,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="378606904"/>
+        <c:crossAx val="233030096"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="378606904"/>
+        <c:axId val="233030096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -985,7 +1076,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="378599456"/>
+        <c:crossAx val="233025784"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -997,6 +1088,38 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="it-IT"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -1049,6 +1172,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="it-IT"/>
+              <a:t>Generational Distance (GD)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
@@ -1083,14 +1231,19 @@
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+        <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>NSGAII</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -1548,14 +1701,19 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
+          <c:tx>
+            <c:v>NSGAII_SI</c:v>
+          </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -1794,7 +1952,7 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1804,11 +1962,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="510494328"/>
-        <c:axId val="510493152"/>
+        <c:axId val="233034408"/>
+        <c:axId val="233027352"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="510494328"/>
+        <c:axId val="233034408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1828,6 +1986,62 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="it-IT"/>
+                  <a:t>Generation</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="it-IT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1865,12 +2079,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="510493152"/>
+        <c:crossAx val="233027352"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="510493152"/>
+        <c:axId val="233027352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1927,7 +2141,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="510494328"/>
+        <c:crossAx val="233034408"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1939,6 +2153,38 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="it-IT"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -1991,6 +2237,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="it-IT"/>
+              <a:t>Hypervolume</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
@@ -2025,14 +2296,19 @@
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+        <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>NSGAII</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -2490,14 +2766,19 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
+          <c:tx>
+            <c:v>NSGAII_SI</c:v>
+          </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -2736,7 +3017,7 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2746,11 +3027,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="378602984"/>
-        <c:axId val="378602592"/>
+        <c:axId val="233033232"/>
+        <c:axId val="233026176"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="378602984"/>
+        <c:axId val="233033232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2770,6 +3051,62 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="it-IT"/>
+                  <a:t>Generation</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="it-IT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2807,12 +3144,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="378602592"/>
+        <c:crossAx val="233026176"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="378602592"/>
+        <c:axId val="233026176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0.65000000000000013"/>
@@ -2870,7 +3207,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="378602984"/>
+        <c:crossAx val="233033232"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2882,6 +3219,38 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="it-IT"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -2934,6 +3303,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="it-IT"/>
+              <a:t>Inverted Generational Distance (IGD)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
@@ -2968,14 +3362,19 @@
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+        <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>NSGAII</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -3433,14 +3832,19 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
+          <c:tx>
+            <c:v>NSGAII_SI</c:v>
+          </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -3679,7 +4083,7 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -3689,11 +4093,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="514295360"/>
-        <c:axId val="514294576"/>
+        <c:axId val="233035192"/>
+        <c:axId val="233024216"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="514295360"/>
+        <c:axId val="233035192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3713,6 +4117,62 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="it-IT"/>
+                  <a:t>Generation</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="it-IT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -3750,12 +4210,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="514294576"/>
+        <c:crossAx val="233024216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="514294576"/>
+        <c:axId val="233024216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3812,7 +4272,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="514295360"/>
+        <c:crossAx val="233035192"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3824,6 +4284,38 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="it-IT"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -3876,6 +4368,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="it-IT"/>
+              <a:t>Spread</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
@@ -3910,14 +4427,19 @@
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+        <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>NSGAII</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -4375,14 +4897,19 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
+          <c:tx>
+            <c:v>NSGAII_SI</c:v>
+          </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -4621,7 +5148,7 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -4631,11 +5158,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="508941704"/>
-        <c:axId val="508941312"/>
+        <c:axId val="233039112"/>
+        <c:axId val="233037936"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="508941704"/>
+        <c:axId val="233039112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4655,6 +5182,62 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="it-IT"/>
+                  <a:t>Generation</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="it-IT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -4692,12 +5275,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="508941312"/>
+        <c:crossAx val="233037936"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="508941312"/>
+        <c:axId val="233037936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4754,7 +5337,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="508941704"/>
+        <c:crossAx val="233039112"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4766,6 +5349,38 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="it-IT"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -7587,16 +8202,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>90487</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7615,6 +8230,725 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6157914" cy="1171576"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3" name="TextBox 2"/>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2733675" y="190500"/>
+              <a:ext cx="6157914" cy="1171576"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑖𝑛</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑑</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>= </m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:nary>
+                          <m:naryPr>
+                            <m:chr m:val="∑"/>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:naryPr>
+                          <m:sub>
+                            <m:r>
+                              <m:rPr>
+                                <m:brk m:alnAt="23"/>
+                              </m:rPr>
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑗</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>=1</m:t>
+                            </m:r>
+                          </m:sub>
+                          <m:sup>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑛𝑟</m:t>
+                            </m:r>
+                          </m:sup>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑖𝑛</m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑑</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑖𝑗</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                        </m:nary>
+                      </m:num>
+                      <m:den>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑛𝑟</m:t>
+                        </m:r>
+                      </m:den>
+                    </m:f>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="it-IT" sz="1400"/>
+            </a:p>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑖𝑛</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑑</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑖𝑠</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑡h𝑒</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑖𝑛𝑑𝑖𝑐𝑎𝑡𝑜𝑟</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑣𝑎𝑙𝑢𝑒</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑓𝑜𝑟</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:sSup>
+                      <m:sSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSupPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑡h</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSup>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑔𝑒𝑛𝑒𝑟𝑎𝑡𝑖𝑜</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>, </m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" sz="1400" b="0" i="1">
+                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              </a:endParaRPr>
+            </a:p>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑛𝑟</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑖𝑠</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑡h𝑒</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑛𝑢𝑚𝑏𝑒𝑟</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑜𝑓</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑟𝑒𝑝𝑒𝑎𝑡𝑖𝑜𝑛</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑜𝑟</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑟𝑢𝑛𝑠</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>, </m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" sz="1400" b="0" i="1">
+                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              </a:endParaRPr>
+            </a:p>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑖𝑛</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑑</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖𝑗</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t> </m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑖𝑠</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑡h𝑒</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑖𝑛𝑑𝑖𝑐𝑎𝑡𝑜𝑟</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑣𝑎𝑙𝑢𝑒</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑜𝑓</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:sSup>
+                      <m:sSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSupPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑡h</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSup>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑔𝑒𝑛𝑒𝑟𝑎𝑡𝑖𝑜𝑛</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑜𝑓</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:sSup>
+                      <m:sSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSupPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑗</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑡h</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSup>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑟𝑢𝑛</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" sz="1400" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3" name="TextBox 2"/>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2733675" y="190500"/>
+              <a:ext cx="6157914" cy="1171576"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1400" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑖𝑛𝑑_𝑖=  (∑_(𝑗=1)^𝑛𝑟▒〖𝑖𝑛𝑑_𝑖𝑗 〗)/𝑛𝑟</a:t>
+              </a:r>
+              <a:endParaRPr lang="it-IT" sz="1400"/>
+            </a:p>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1400" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑖𝑛𝑑_𝑖  𝑖𝑠 𝑡ℎ𝑒 𝑖𝑛𝑑𝑖𝑐𝑎𝑡𝑜𝑟 𝑣𝑎𝑙𝑢𝑒 𝑓𝑜𝑟 𝑖^𝑡ℎ 𝑔𝑒𝑛𝑒𝑟𝑎𝑡𝑖𝑜, </a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" sz="1400" b="0" i="1">
+                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              </a:endParaRPr>
+            </a:p>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1400" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑛𝑟 𝑖𝑠 𝑡ℎ𝑒 𝑛𝑢𝑚𝑏𝑒𝑟 𝑜𝑓 𝑟𝑒𝑝𝑒𝑎𝑡𝑖𝑜𝑛 𝑜𝑟 𝑟𝑢𝑛𝑠, </a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" sz="1400" b="0" i="1">
+                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              </a:endParaRPr>
+            </a:p>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1400" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑖𝑛𝑑_(𝑖𝑗 ) 𝑖𝑠 𝑡ℎ𝑒 𝑖𝑛𝑑𝑖𝑐𝑎𝑡𝑜𝑟 𝑣𝑎𝑙𝑢𝑒 𝑜𝑓 𝑖^𝑡ℎ 𝑔𝑒𝑛𝑒𝑟𝑎𝑡𝑖𝑜𝑛 𝑜𝑓 𝑗^𝑡ℎ 𝑟𝑢𝑛</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" sz="1400" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7622,16 +8956,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>90487</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7657,16 +8991,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>90487</xdr:rowOff>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7692,16 +9026,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>90487</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>185737</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7727,16 +9061,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>90487</xdr:rowOff>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>33337</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8025,14 +9359,14 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="2"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
@@ -9030,14 +10364,14 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="2"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
@@ -9231,7 +10565,7 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="1">
         <v>9.0883116938525303E-4</v>
       </c>
     </row>
@@ -9239,13 +10573,13 @@
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="1">
         <v>9.2253163283763796E-4</v>
       </c>
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="1">
         <v>8.3438221475302097E-4</v>
       </c>
     </row>
@@ -9253,13 +10587,13 @@
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="1">
         <v>8.47669526110021E-4</v>
       </c>
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="1">
         <v>7.80675983803895E-4</v>
       </c>
     </row>
@@ -9267,13 +10601,13 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="1">
         <v>7.9150650370939601E-4</v>
       </c>
       <c r="C18">
         <v>17</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="1">
         <v>7.2276514432390395E-4</v>
       </c>
     </row>
@@ -9281,13 +10615,13 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="1">
         <v>7.48181500298473E-4</v>
       </c>
       <c r="C19">
         <v>18</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="1">
         <v>6.9008205560913997E-4</v>
       </c>
     </row>
@@ -9295,13 +10629,13 @@
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="1">
         <v>7.1114687764625695E-4</v>
       </c>
       <c r="C20">
         <v>19</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="1">
         <v>6.5433151134782397E-4</v>
       </c>
     </row>
@@ -9309,13 +10643,13 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="1">
         <v>6.6228085214212803E-4</v>
       </c>
       <c r="C21">
         <v>20</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="1">
         <v>6.1155745660518095E-4</v>
       </c>
     </row>
@@ -9323,13 +10657,13 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="1">
         <v>6.2125290056156996E-4</v>
       </c>
       <c r="C22">
         <v>21</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="1">
         <v>5.7418792124796895E-4</v>
       </c>
     </row>
@@ -9337,13 +10671,13 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="1">
         <v>5.6890341188297103E-4</v>
       </c>
       <c r="C23">
         <v>22</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="1">
         <v>5.3080696486497198E-4</v>
       </c>
     </row>
@@ -9351,13 +10685,13 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="1">
         <v>5.4779069296664602E-4</v>
       </c>
       <c r="C24">
         <v>23</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="1">
         <v>5.1688082885305395E-4</v>
       </c>
     </row>
@@ -9365,13 +10699,13 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="1">
         <v>5.1802121603684295E-4</v>
       </c>
       <c r="C25">
         <v>24</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="1">
         <v>4.9627885904685997E-4</v>
       </c>
     </row>
@@ -9379,13 +10713,13 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="1">
         <v>4.8499376756276001E-4</v>
       </c>
       <c r="C26">
         <v>25</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="1">
         <v>4.7774379937558898E-4</v>
       </c>
     </row>
@@ -9393,13 +10727,13 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="1">
         <v>4.6879331197938098E-4</v>
       </c>
       <c r="C27">
         <v>26</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="1">
         <v>4.6897708181837801E-4</v>
       </c>
     </row>
@@ -9407,13 +10741,13 @@
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="1">
         <v>4.57283968382422E-4</v>
       </c>
       <c r="C28">
         <v>27</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="1">
         <v>4.6344539457096601E-4</v>
       </c>
     </row>
@@ -9421,13 +10755,13 @@
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="1">
         <v>4.24900547165198E-4</v>
       </c>
       <c r="C29">
         <v>28</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="1">
         <v>4.5712133385636899E-4</v>
       </c>
     </row>
@@ -9435,13 +10769,13 @@
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30" s="1">
         <v>4.20908913669575E-4</v>
       </c>
       <c r="C30">
         <v>29</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="1">
         <v>4.4714806172369302E-4</v>
       </c>
     </row>
@@ -9449,13 +10783,13 @@
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="1">
         <v>4.05614331960135E-4</v>
       </c>
       <c r="C31">
         <v>30</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="1">
         <v>4.3424867606708999E-4</v>
       </c>
     </row>
@@ -9463,13 +10797,13 @@
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="1">
         <v>3.8480583313421402E-4</v>
       </c>
       <c r="C32">
         <v>31</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="1">
         <v>4.1990890500149299E-4</v>
       </c>
     </row>
@@ -9477,13 +10811,13 @@
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="1">
         <v>3.68814584498239E-4</v>
       </c>
       <c r="C33">
         <v>32</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="1">
         <v>4.08127887148878E-4</v>
       </c>
     </row>
@@ -9491,13 +10825,13 @@
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="1">
         <v>3.5787141233278999E-4</v>
       </c>
       <c r="C34">
         <v>33</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="1">
         <v>3.9949651889824203E-4</v>
       </c>
     </row>
@@ -9505,13 +10839,13 @@
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="1">
         <v>3.5082951848556501E-4</v>
       </c>
       <c r="C35">
         <v>34</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="1">
         <v>4.01170572958099E-4</v>
       </c>
     </row>
@@ -9519,13 +10853,13 @@
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="1">
         <v>3.5102780908237901E-4</v>
       </c>
       <c r="C36">
         <v>35</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="1">
         <v>4.0429476296078399E-4</v>
       </c>
     </row>
@@ -9533,13 +10867,13 @@
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="1">
         <v>3.4800927330132703E-4</v>
       </c>
       <c r="C37">
         <v>36</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="1">
         <v>4.1313147620511902E-4</v>
       </c>
     </row>
@@ -9547,13 +10881,13 @@
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="1">
         <v>3.5367302098830602E-4</v>
       </c>
       <c r="C38">
         <v>37</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="1">
         <v>4.1239352929854802E-4</v>
       </c>
     </row>
@@ -9561,13 +10895,13 @@
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="1">
         <v>3.4944995019321398E-4</v>
       </c>
       <c r="C39">
         <v>38</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39" s="1">
         <v>4.1656672140509901E-4</v>
       </c>
     </row>
@@ -9575,13 +10909,13 @@
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40" s="1">
         <v>3.5658767991817298E-4</v>
       </c>
       <c r="C40">
         <v>39</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="1">
         <v>3.9622777619184498E-4</v>
       </c>
     </row>
@@ -9589,13 +10923,13 @@
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="1">
         <v>3.5012071970403502E-4</v>
       </c>
       <c r="C41">
         <v>40</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="1">
         <v>3.9097798132477598E-4</v>
       </c>
     </row>
@@ -9603,13 +10937,13 @@
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42" s="1">
         <v>3.3646307805431801E-4</v>
       </c>
       <c r="C42">
         <v>41</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="1">
         <v>4.0155308482939201E-4</v>
       </c>
     </row>
@@ -9617,13 +10951,13 @@
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="1">
         <v>3.3880208589706298E-4</v>
       </c>
       <c r="C43">
         <v>42</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="1">
         <v>3.95903884011385E-4</v>
       </c>
     </row>
@@ -9631,13 +10965,13 @@
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="1">
         <v>3.3657289854348402E-4</v>
       </c>
       <c r="C44">
         <v>43</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="1">
         <v>3.9830389304178898E-4</v>
       </c>
     </row>
@@ -9645,13 +10979,13 @@
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="1">
         <v>3.38396341422133E-4</v>
       </c>
       <c r="C45">
         <v>44</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="1">
         <v>3.9288132404300498E-4</v>
       </c>
     </row>
@@ -9659,13 +10993,13 @@
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" s="2">
+      <c r="B46" s="1">
         <v>3.4086490485094999E-4</v>
       </c>
       <c r="C46">
         <v>45</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="1">
         <v>3.9927963442358099E-4</v>
       </c>
     </row>
@@ -9673,13 +11007,13 @@
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47" s="1">
         <v>3.31339641448088E-4</v>
       </c>
       <c r="C47">
         <v>46</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="1">
         <v>3.8739548534710399E-4</v>
       </c>
     </row>
@@ -9687,13 +11021,13 @@
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48" s="1">
         <v>3.1979769174208698E-4</v>
       </c>
       <c r="C48">
         <v>47</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="1">
         <v>3.91261413778322E-4</v>
       </c>
     </row>
@@ -9701,13 +11035,13 @@
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="1">
         <v>3.1633147739676501E-4</v>
       </c>
       <c r="C49">
         <v>48</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="1">
         <v>3.9451120698353801E-4</v>
       </c>
     </row>
@@ -9715,13 +11049,13 @@
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50" s="1">
         <v>3.1904142562728997E-4</v>
       </c>
       <c r="C50">
         <v>49</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="1">
         <v>3.9038156859295199E-4</v>
       </c>
     </row>
@@ -9729,13 +11063,13 @@
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="1">
         <v>3.1524407852689002E-4</v>
       </c>
       <c r="C51">
         <v>50</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="1">
         <v>3.8622455702593401E-4</v>
       </c>
     </row>
@@ -9743,13 +11077,13 @@
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52" s="1">
         <v>3.1398976210366601E-4</v>
       </c>
       <c r="C52">
         <v>51</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52" s="1">
         <v>3.8946630727969901E-4</v>
       </c>
     </row>
@@ -9757,13 +11091,13 @@
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" s="1">
         <v>3.1228635063619E-4</v>
       </c>
       <c r="C53">
         <v>52</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D53" s="1">
         <v>3.7631392000020701E-4</v>
       </c>
     </row>
@@ -9771,13 +11105,13 @@
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54" s="1">
         <v>3.1621012869359499E-4</v>
       </c>
       <c r="C54">
         <v>53</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54" s="1">
         <v>3.7719577190108898E-4</v>
       </c>
     </row>
@@ -9785,13 +11119,13 @@
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55" s="1">
         <v>3.0798713378064901E-4</v>
       </c>
       <c r="C55">
         <v>54</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D55" s="1">
         <v>3.8028280381384802E-4</v>
       </c>
     </row>
@@ -9799,13 +11133,13 @@
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="1">
         <v>3.16211758354541E-4</v>
       </c>
       <c r="C56">
         <v>55</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56" s="1">
         <v>3.8233539870019198E-4</v>
       </c>
     </row>
@@ -9813,13 +11147,13 @@
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57" s="1">
         <v>3.1279779739524702E-4</v>
       </c>
       <c r="C57">
         <v>56</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D57" s="1">
         <v>3.8383433552139002E-4</v>
       </c>
     </row>
@@ -9827,13 +11161,13 @@
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B58" s="1">
         <v>3.12885506473467E-4</v>
       </c>
       <c r="C58">
         <v>57</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58" s="1">
         <v>3.8097738739993901E-4</v>
       </c>
     </row>
@@ -9841,13 +11175,13 @@
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59" s="1">
         <v>3.1140773317617503E-4</v>
       </c>
       <c r="C59">
         <v>58</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59" s="1">
         <v>3.8222149940857902E-4</v>
       </c>
     </row>
@@ -9855,13 +11189,13 @@
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60" s="1">
         <v>3.1206531355423199E-4</v>
       </c>
       <c r="C60">
         <v>59</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60" s="1">
         <v>3.78760028931395E-4</v>
       </c>
     </row>
@@ -9869,13 +11203,13 @@
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61" s="1">
         <v>3.1623898762415102E-4</v>
       </c>
       <c r="C61">
         <v>60</v>
       </c>
-      <c r="D61" s="2">
+      <c r="D61" s="1">
         <v>3.7455425911435598E-4</v>
       </c>
     </row>
@@ -9883,13 +11217,13 @@
       <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" s="2">
+      <c r="B62" s="1">
         <v>3.0798550473855102E-4</v>
       </c>
       <c r="C62">
         <v>61</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62" s="1">
         <v>3.7072332230313697E-4</v>
       </c>
     </row>
@@ -9897,13 +11231,13 @@
       <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" s="2">
+      <c r="B63" s="1">
         <v>3.08075534056743E-4</v>
       </c>
       <c r="C63">
         <v>62</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D63" s="1">
         <v>3.6316677801223601E-4</v>
       </c>
     </row>
@@ -9911,13 +11245,13 @@
       <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" s="2">
+      <c r="B64" s="1">
         <v>3.04940745985122E-4</v>
       </c>
       <c r="C64">
         <v>63</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64" s="1">
         <v>3.5427950006193803E-4</v>
       </c>
     </row>
@@ -9925,13 +11259,13 @@
       <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" s="2">
+      <c r="B65" s="1">
         <v>3.0519287959425098E-4</v>
       </c>
       <c r="C65">
         <v>64</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65" s="1">
         <v>3.5098998913497299E-4</v>
       </c>
     </row>
@@ -9939,13 +11273,13 @@
       <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" s="2">
+      <c r="B66" s="1">
         <v>3.12792705353473E-4</v>
       </c>
       <c r="C66">
         <v>65</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D66" s="1">
         <v>3.4879522474423499E-4</v>
       </c>
     </row>
@@ -9953,13 +11287,13 @@
       <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" s="2">
+      <c r="B67" s="1">
         <v>3.0113278074980299E-4</v>
       </c>
       <c r="C67">
         <v>66</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="1">
         <v>3.6394457758151701E-4</v>
       </c>
     </row>
@@ -9967,13 +11301,13 @@
       <c r="A68">
         <v>67</v>
       </c>
-      <c r="B68" s="2">
+      <c r="B68" s="1">
         <v>3.0180922307701698E-4</v>
       </c>
       <c r="C68">
         <v>67</v>
       </c>
-      <c r="D68" s="2">
+      <c r="D68" s="1">
         <v>3.5337792221981401E-4</v>
       </c>
     </row>
@@ -9981,13 +11315,13 @@
       <c r="A69">
         <v>68</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B69" s="1">
         <v>2.9598180197460902E-4</v>
       </c>
       <c r="C69">
         <v>68</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D69" s="1">
         <v>3.4898961428167502E-4</v>
       </c>
     </row>
@@ -9995,13 +11329,13 @@
       <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70" s="2">
+      <c r="B70" s="1">
         <v>2.9677232784032102E-4</v>
       </c>
       <c r="C70">
         <v>69</v>
       </c>
-      <c r="D70" s="2">
+      <c r="D70" s="1">
         <v>3.4365049754743297E-4</v>
       </c>
     </row>
@@ -10009,13 +11343,13 @@
       <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" s="2">
+      <c r="B71" s="1">
         <v>2.9019498285911302E-4</v>
       </c>
       <c r="C71">
         <v>70</v>
       </c>
-      <c r="D71" s="2">
+      <c r="D71" s="1">
         <v>3.45993353399636E-4</v>
       </c>
     </row>
@@ -10035,14 +11369,14 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="2"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
@@ -11040,14 +12374,14 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="2"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
@@ -12045,14 +13379,14 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="2"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">

--- a/InitializationResults/WithTrack/Comparison of NSGAII with NSGAII_SI for each generation (on average).xlsx
+++ b/InitializationResults/WithTrack/Comparison of NSGAII with NSGAII_SI for each generation (on average).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="10995"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="10995" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="EPS" sheetId="1" r:id="rId1"/>
@@ -580,25 +580,25 @@
                   <c:v>8.5</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>7.9052999999999898</c:v>
+                  <c:v>7.90519999999999</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>7.6043000000000003</c:v>
+                  <c:v>7.6048</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>6.7077999999999998</c:v>
+                  <c:v>6.7077</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>6.7045999999999903</c:v>
+                  <c:v>6.7045000000000003</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>6.6041999999999996</c:v>
+                  <c:v>6.6044999999999998</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>6.5042</c:v>
+                  <c:v>6.5045000000000002</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>5.9040999999999997</c:v>
+                  <c:v>5.9042000000000003</c:v>
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>5.2054999999999998</c:v>
@@ -607,22 +607,22 @@
                   <c:v>4.8055000000000003</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>4.8040000000000003</c:v>
+                  <c:v>4.8037000000000001</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>4.7052999999999896</c:v>
+                  <c:v>4.7051999999999996</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>4.7052999999999896</c:v>
+                  <c:v>4.7051999999999996</c:v>
                 </c:pt>
                 <c:pt idx="64">
+                  <c:v>4.7039999999999997</c:v>
+                </c:pt>
+                <c:pt idx="65">
                   <c:v>4.7039</c:v>
                 </c:pt>
-                <c:pt idx="65">
-                  <c:v>4.7036999999999898</c:v>
-                </c:pt>
                 <c:pt idx="66">
-                  <c:v>4.6044999999999998</c:v>
+                  <c:v>4.6045999999999996</c:v>
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>4.6033999999999997</c:v>
@@ -675,214 +675,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>717.8</c:v>
+                  <c:v>387.4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>581.6</c:v>
+                  <c:v>311.7</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>482.1</c:v>
+                  <c:v>244.7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>453.3</c:v>
+                  <c:v>196.9</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>390</c:v>
+                  <c:v>184.2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>337.5</c:v>
+                  <c:v>167.2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>282.8</c:v>
+                  <c:v>152.80000000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>239.1</c:v>
+                  <c:v>126.1</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>214</c:v>
+                  <c:v>122</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>208.8</c:v>
+                  <c:v>117</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>177</c:v>
+                  <c:v>97.8</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>159.69999999999999</c:v>
+                  <c:v>86.2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>134.80000000000001</c:v>
+                  <c:v>79.8</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>130</c:v>
+                  <c:v>67.400000000000006</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>116.8</c:v>
+                  <c:v>63.2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>100</c:v>
+                  <c:v>57.8</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>98</c:v>
+                  <c:v>54.3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>93.2</c:v>
+                  <c:v>46.2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>83.9</c:v>
+                  <c:v>45.2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>76</c:v>
+                  <c:v>42.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>68.5</c:v>
+                  <c:v>40.200000000000003</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>66.7</c:v>
+                  <c:v>39.1</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>59.5</c:v>
+                  <c:v>37.700000000000003</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>56</c:v>
+                  <c:v>35.4</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>49.5</c:v>
+                  <c:v>29.7</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>42.6</c:v>
+                  <c:v>28.1</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>37.1</c:v>
+                  <c:v>25.4</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>33.5</c:v>
+                  <c:v>24.6</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>33.5</c:v>
+                  <c:v>21.6</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>31.6</c:v>
+                  <c:v>20.399999999999999</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>31.2</c:v>
+                  <c:v>20.100000000000001</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>25.3</c:v>
+                  <c:v>17.399999999999999</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>24.7</c:v>
+                  <c:v>17.399999999999999</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>21.6</c:v>
+                  <c:v>16.5</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>21.6</c:v>
+                  <c:v>15.7</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>18.899999999999999</c:v>
+                  <c:v>14.3</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>18.2</c:v>
+                  <c:v>12.4</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>17.7</c:v>
+                  <c:v>11.7</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>17.600000000000001</c:v>
+                  <c:v>11.1</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>16.5</c:v>
+                  <c:v>10.4</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>16.5</c:v>
+                  <c:v>9.6999999999999993</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>16.399999999999999</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>14.3</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>12.4</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>12.4</c:v>
+                  <c:v>8.6</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>11.6</c:v>
+                  <c:v>8.6</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>10.5</c:v>
+                  <c:v>8.1999999999999993</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>10.1</c:v>
+                  <c:v>8.1999999999999993</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>9.3000000000000007</c:v>
+                  <c:v>7.8</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>8.5</c:v>
+                  <c:v>6.5</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>8.1</c:v>
+                  <c:v>6.4</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>7</c:v>
+                  <c:v>6.4</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>6.4</c:v>
+                  <c:v>6.1</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>6.3</c:v>
+                  <c:v>5.2039</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>5.8</c:v>
+                  <c:v>5.1048</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>5.4</c:v>
+                  <c:v>4.3048000000000002</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>5.0999999999999996</c:v>
+                  <c:v>4.3051000000000004</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>5</c:v>
+                  <c:v>4.1054000000000004</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>5</c:v>
+                  <c:v>4.1051000000000002</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>4.9000000000000004</c:v>
+                  <c:v>4.0050999999999997</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>4.5</c:v>
+                  <c:v>3.9045000000000001</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>3.8</c:v>
+                  <c:v>3.7058</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>3.4039000000000001</c:v>
+                  <c:v>3.7058</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>2.9037999999999999</c:v>
+                  <c:v>3.5093000000000001</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>2.7042999999999999</c:v>
+                  <c:v>3.4152999999999998</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>2.6067</c:v>
+                  <c:v>3.2141999999999902</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>2.6067</c:v>
+                  <c:v>3.0137</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>2.5050999999999899</c:v>
+                  <c:v>2.9127999999999998</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>2.2050999999999998</c:v>
+                  <c:v>2.8128000000000002</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>2.1042000000000001</c:v>
+                  <c:v>2.7111000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -897,11 +897,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="233025784"/>
-        <c:axId val="233030096"/>
+        <c:axId val="346524912"/>
+        <c:axId val="346532360"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="233025784"/>
+        <c:axId val="346524912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1014,12 +1014,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="233030096"/>
+        <c:crossAx val="346532360"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="233030096"/>
+        <c:axId val="346532360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1076,7 +1076,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="233025784"/>
+        <c:crossAx val="346524912"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1489,214 +1489,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>8.6474210885704103E-3</c:v>
+                  <c:v>8.6238154451302295E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.97459970716292E-3</c:v>
+                  <c:v>6.9493374459024902E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.8356701598041702E-3</c:v>
+                  <c:v>5.8135592505184604E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.6643627179502496E-3</c:v>
+                  <c:v>4.6438771725312803E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.1485347585777897E-3</c:v>
+                  <c:v>4.1269211164086097E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.3519807553477401E-3</c:v>
+                  <c:v>3.3344745739752901E-3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.9944450997469998E-3</c:v>
+                  <c:v>2.9808691587765298E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.4400331965300699E-3</c:v>
+                  <c:v>2.4289087630244201E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.0743917265516202E-3</c:v>
+                  <c:v>2.06211627272612E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.78275308947511E-3</c:v>
+                  <c:v>1.7727286221109299E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.59281646378411E-3</c:v>
+                  <c:v>1.58167746719226E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.37175510700166E-3</c:v>
+                  <c:v>1.3602928802401301E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.1863949707377501E-3</c:v>
+                  <c:v>1.17601729199454E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.0461775114207401E-3</c:v>
+                  <c:v>1.03768341005777E-3</c:v>
                 </c:pt>
                 <c:pt idx="14" formatCode="0.00E+00">
-                  <c:v>9.2253163283763796E-4</c:v>
+                  <c:v>9.1338433016364203E-4</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00E+00">
-                  <c:v>8.47669526110021E-4</c:v>
+                  <c:v>8.3714619276021305E-4</c:v>
                 </c:pt>
                 <c:pt idx="16" formatCode="0.00E+00">
-                  <c:v>7.9150650370939601E-4</c:v>
+                  <c:v>7.8464288313204601E-4</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="0.00E+00">
-                  <c:v>7.48181500298473E-4</c:v>
+                  <c:v>7.3980277889194499E-4</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00E+00">
-                  <c:v>7.1114687764625695E-4</c:v>
+                  <c:v>7.0377031857641302E-4</c:v>
                 </c:pt>
                 <c:pt idx="19" formatCode="0.00E+00">
-                  <c:v>6.6228085214212803E-4</c:v>
+                  <c:v>6.5534414879862195E-4</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="0.00E+00">
-                  <c:v>6.2125290056156996E-4</c:v>
+                  <c:v>6.1391868205965005E-4</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00E+00">
-                  <c:v>5.6890341188297103E-4</c:v>
+                  <c:v>5.5993713950838796E-4</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="0.00E+00">
-                  <c:v>5.4779069296664602E-4</c:v>
+                  <c:v>5.4108139995146095E-4</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="0.00E+00">
-                  <c:v>5.1802121603684295E-4</c:v>
+                  <c:v>5.1169062633122297E-4</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00E+00">
-                  <c:v>4.8499376756276001E-4</c:v>
+                  <c:v>4.77852625756747E-4</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="0.00E+00">
-                  <c:v>4.6879331197938098E-4</c:v>
+                  <c:v>4.6215836511428798E-4</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="0.00E+00">
-                  <c:v>4.57283968382422E-4</c:v>
+                  <c:v>4.5274404144553699E-4</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00E+00">
-                  <c:v>4.24900547165198E-4</c:v>
+                  <c:v>4.2232676484324402E-4</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="0.00E+00">
-                  <c:v>4.20908913669575E-4</c:v>
+                  <c:v>4.1568668910077602E-4</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="0.00E+00">
-                  <c:v>4.05614331960135E-4</c:v>
+                  <c:v>4.0237079682418599E-4</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00E+00">
-                  <c:v>3.8480583313421402E-4</c:v>
+                  <c:v>3.81095776479886E-4</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="0.00E+00">
-                  <c:v>3.68814584498239E-4</c:v>
+                  <c:v>3.6681549408278699E-4</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="0.00E+00">
-                  <c:v>3.5787141233278999E-4</c:v>
+                  <c:v>3.5414776590699399E-4</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00E+00">
-                  <c:v>3.5082951848556501E-4</c:v>
+                  <c:v>3.4787215523345602E-4</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="0.00E+00">
-                  <c:v>3.5102780908237901E-4</c:v>
+                  <c:v>3.4451959389052497E-4</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="0.00E+00">
-                  <c:v>3.4800927330132703E-4</c:v>
+                  <c:v>3.42780085589735E-4</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00E+00">
-                  <c:v>3.5367302098830602E-4</c:v>
+                  <c:v>3.4739502557412199E-4</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="0.00E+00">
-                  <c:v>3.4944995019321398E-4</c:v>
+                  <c:v>3.4498752343934698E-4</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="0.00E+00">
-                  <c:v>3.5658767991817298E-4</c:v>
+                  <c:v>3.48219179440788E-4</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00E+00">
-                  <c:v>3.5012071970403502E-4</c:v>
+                  <c:v>3.4257667715137998E-4</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="0.00E+00">
-                  <c:v>3.3646307805431801E-4</c:v>
+                  <c:v>3.2941801669786401E-4</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="0.00E+00">
-                  <c:v>3.3880208589706298E-4</c:v>
+                  <c:v>3.3081987079039801E-4</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00E+00">
-                  <c:v>3.3657289854348402E-4</c:v>
+                  <c:v>3.2857429530746001E-4</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="0.00E+00">
-                  <c:v>3.38396341422133E-4</c:v>
+                  <c:v>3.30348036914934E-4</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="0.00E+00">
-                  <c:v>3.4086490485094999E-4</c:v>
+                  <c:v>3.3174256342686403E-4</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00E+00">
-                  <c:v>3.31339641448088E-4</c:v>
+                  <c:v>3.2166727483059999E-4</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="0.00E+00">
-                  <c:v>3.1979769174208698E-4</c:v>
+                  <c:v>3.1035298959514602E-4</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="0.00E+00">
-                  <c:v>3.1633147739676501E-4</c:v>
+                  <c:v>3.0662098407074402E-4</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00E+00">
-                  <c:v>3.1904142562728997E-4</c:v>
+                  <c:v>3.1006985954753103E-4</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="0.00E+00">
-                  <c:v>3.1524407852689002E-4</c:v>
+                  <c:v>3.0741872872216302E-4</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="0.00E+00">
-                  <c:v>3.1398976210366601E-4</c:v>
+                  <c:v>3.0512274614305599E-4</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00E+00">
-                  <c:v>3.1228635063619E-4</c:v>
+                  <c:v>3.0335668383452401E-4</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="0.00E+00">
-                  <c:v>3.1621012869359499E-4</c:v>
+                  <c:v>3.0751836824008199E-4</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="0.00E+00">
-                  <c:v>3.0798713378064901E-4</c:v>
+                  <c:v>2.99613913546561E-4</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00E+00">
-                  <c:v>3.16211758354541E-4</c:v>
+                  <c:v>3.1014797633432701E-4</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00E+00">
-                  <c:v>3.1279779739524702E-4</c:v>
+                  <c:v>3.07479503562066E-4</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00E+00">
-                  <c:v>3.12885506473467E-4</c:v>
+                  <c:v>3.0644010509891102E-4</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00E+00">
-                  <c:v>3.1140773317617503E-4</c:v>
+                  <c:v>3.0417122419283601E-4</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00E+00">
-                  <c:v>3.1206531355423199E-4</c:v>
+                  <c:v>3.0504684849950298E-4</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00E+00">
-                  <c:v>3.1623898762415102E-4</c:v>
+                  <c:v>3.1087107174923502E-4</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="0.00E+00">
-                  <c:v>3.0798550473855102E-4</c:v>
+                  <c:v>3.0149487324967702E-4</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="0.00E+00">
-                  <c:v>3.08075534056743E-4</c:v>
+                  <c:v>3.0255436832057702E-4</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="0.00E+00">
-                  <c:v>3.04940745985122E-4</c:v>
+                  <c:v>2.97438729777713E-4</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="0.00E+00">
-                  <c:v>3.0519287959425098E-4</c:v>
+                  <c:v>2.9753249213139302E-4</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="0.00E+00">
-                  <c:v>3.12792705353473E-4</c:v>
+                  <c:v>3.0660315413073901E-4</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.00E+00">
-                  <c:v>3.0113278074980299E-4</c:v>
+                  <c:v>2.9766167949058902E-4</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="0.00E+00">
-                  <c:v>3.0180922307701698E-4</c:v>
+                  <c:v>2.9649910020974001E-4</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="0.00E+00">
-                  <c:v>2.9598180197460902E-4</c:v>
+                  <c:v>2.9084415349995597E-4</c:v>
                 </c:pt>
                 <c:pt idx="68" formatCode="0.00E+00">
-                  <c:v>2.9677232784032102E-4</c:v>
+                  <c:v>2.9149113701476098E-4</c:v>
                 </c:pt>
                 <c:pt idx="69" formatCode="0.00E+00">
-                  <c:v>2.9019498285911302E-4</c:v>
+                  <c:v>2.88870859121283E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1740,214 +1740,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>1.40112913580365E-2</c:v>
+                  <c:v>1.1159649179412401E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.8266292191054602E-3</c:v>
+                  <c:v>7.9365973298077108E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.0964271569460497E-3</c:v>
+                  <c:v>5.5631305807959898E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.07279307842205E-3</c:v>
+                  <c:v>4.2111813759793497E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.95987884099731E-3</c:v>
+                  <c:v>3.0404625080717499E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.1673688946447101E-3</c:v>
+                  <c:v>2.3215111549507502E-3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.5228099155473302E-3</c:v>
+                  <c:v>1.8586010019362199E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.1714629111952701E-3</c:v>
+                  <c:v>1.4185622928898601E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.75806982359715E-3</c:v>
+                  <c:v>1.1626559016751001E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.4952954162514201E-3</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1.30525868999047E-3</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1.1814921525444299E-3</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1.0537908140483001E-3</c:v>
+                  <c:v>1.0298255071569699E-3</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0.00E+00">
+                  <c:v>9.1545133228479502E-4</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="0.00E+00">
+                  <c:v>8.0900468996901497E-4</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0.00E+00">
+                  <c:v>7.5551518540957995E-4</c:v>
                 </c:pt>
                 <c:pt idx="13" formatCode="0.00E+00">
-                  <c:v>9.0883116938525303E-4</c:v>
+                  <c:v>6.7220636025611298E-4</c:v>
                 </c:pt>
                 <c:pt idx="14" formatCode="0.00E+00">
-                  <c:v>8.3438221475302097E-4</c:v>
+                  <c:v>6.2925969887452798E-4</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00E+00">
-                  <c:v>7.80675983803895E-4</c:v>
+                  <c:v>5.9935016274222802E-4</c:v>
                 </c:pt>
                 <c:pt idx="16" formatCode="0.00E+00">
-                  <c:v>7.2276514432390395E-4</c:v>
+                  <c:v>5.5349477484964698E-4</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="0.00E+00">
-                  <c:v>6.9008205560913997E-4</c:v>
+                  <c:v>5.3927534346311502E-4</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00E+00">
-                  <c:v>6.5433151134782397E-4</c:v>
+                  <c:v>5.1743336242093103E-4</c:v>
                 </c:pt>
                 <c:pt idx="19" formatCode="0.00E+00">
-                  <c:v>6.1155745660518095E-4</c:v>
+                  <c:v>5.05424955588505E-4</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="0.00E+00">
-                  <c:v>5.7418792124796895E-4</c:v>
+                  <c:v>4.8916484149419696E-4</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00E+00">
-                  <c:v>5.3080696486497198E-4</c:v>
+                  <c:v>4.7137771584760302E-4</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="0.00E+00">
-                  <c:v>5.1688082885305395E-4</c:v>
+                  <c:v>4.57792145933761E-4</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="0.00E+00">
-                  <c:v>4.9627885904685997E-4</c:v>
+                  <c:v>4.4125051882311399E-4</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00E+00">
-                  <c:v>4.7774379937558898E-4</c:v>
+                  <c:v>4.1686210379794701E-4</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="0.00E+00">
-                  <c:v>4.6897708181837801E-4</c:v>
+                  <c:v>4.0386111111341902E-4</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="0.00E+00">
-                  <c:v>4.6344539457096601E-4</c:v>
+                  <c:v>3.9405328869416E-4</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00E+00">
-                  <c:v>4.5712133385636899E-4</c:v>
+                  <c:v>3.9126379285902099E-4</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="0.00E+00">
-                  <c:v>4.4714806172369302E-4</c:v>
+                  <c:v>3.8610311717891002E-4</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="0.00E+00">
-                  <c:v>4.3424867606708999E-4</c:v>
+                  <c:v>3.8418442587055099E-4</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00E+00">
-                  <c:v>4.1990890500149299E-4</c:v>
+                  <c:v>3.7306746478879999E-4</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="0.00E+00">
-                  <c:v>4.08127887148878E-4</c:v>
+                  <c:v>3.7533156528957699E-4</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="0.00E+00">
-                  <c:v>3.9949651889824203E-4</c:v>
+                  <c:v>3.6748909317515903E-4</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00E+00">
-                  <c:v>4.01170572958099E-4</c:v>
+                  <c:v>3.6503228597748702E-4</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="0.00E+00">
-                  <c:v>4.0429476296078399E-4</c:v>
+                  <c:v>3.5653113592081501E-4</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="0.00E+00">
-                  <c:v>4.1313147620511902E-4</c:v>
+                  <c:v>3.5589290463310401E-4</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00E+00">
-                  <c:v>4.1239352929854802E-4</c:v>
+                  <c:v>3.56447258703549E-4</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="0.00E+00">
-                  <c:v>4.1656672140509901E-4</c:v>
+                  <c:v>3.57555889536875E-4</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="0.00E+00">
-                  <c:v>3.9622777619184498E-4</c:v>
+                  <c:v>3.6003311609356098E-4</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00E+00">
-                  <c:v>3.9097798132477598E-4</c:v>
+                  <c:v>3.5576098203152299E-4</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="0.00E+00">
-                  <c:v>4.0155308482939201E-4</c:v>
+                  <c:v>3.5252434100742803E-4</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="0.00E+00">
-                  <c:v>3.95903884011385E-4</c:v>
+                  <c:v>3.48061943014089E-4</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00E+00">
-                  <c:v>3.9830389304178898E-4</c:v>
+                  <c:v>3.5504635858424902E-4</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="0.00E+00">
-                  <c:v>3.9288132404300498E-4</c:v>
+                  <c:v>3.5554445758511201E-4</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="0.00E+00">
-                  <c:v>3.9927963442358099E-4</c:v>
+                  <c:v>3.5217000114907699E-4</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00E+00">
-                  <c:v>3.8739548534710399E-4</c:v>
+                  <c:v>3.4478517115087501E-4</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="0.00E+00">
-                  <c:v>3.91261413778322E-4</c:v>
+                  <c:v>3.4450792543391703E-4</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="0.00E+00">
-                  <c:v>3.9451120698353801E-4</c:v>
+                  <c:v>3.4967363520832197E-4</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00E+00">
-                  <c:v>3.9038156859295199E-4</c:v>
+                  <c:v>3.41057159787945E-4</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="0.00E+00">
-                  <c:v>3.8622455702593401E-4</c:v>
+                  <c:v>3.5092827219385499E-4</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="0.00E+00">
-                  <c:v>3.8946630727969901E-4</c:v>
+                  <c:v>3.4671952436666998E-4</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00E+00">
-                  <c:v>3.7631392000020701E-4</c:v>
+                  <c:v>3.3554561058928597E-4</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="0.00E+00">
-                  <c:v>3.7719577190108898E-4</c:v>
+                  <c:v>3.2695296051417502E-4</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="0.00E+00">
-                  <c:v>3.8028280381384802E-4</c:v>
+                  <c:v>3.2719746783496098E-4</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00E+00">
-                  <c:v>3.8233539870019198E-4</c:v>
+                  <c:v>3.27473703643635E-4</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00E+00">
-                  <c:v>3.8383433552139002E-4</c:v>
+                  <c:v>3.1815063043047102E-4</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00E+00">
-                  <c:v>3.8097738739993901E-4</c:v>
+                  <c:v>3.2735932898918702E-4</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00E+00">
-                  <c:v>3.8222149940857902E-4</c:v>
+                  <c:v>3.2650772858947897E-4</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00E+00">
-                  <c:v>3.78760028931395E-4</c:v>
+                  <c:v>3.2715330616477198E-4</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00E+00">
-                  <c:v>3.7455425911435598E-4</c:v>
+                  <c:v>3.26119143384753E-4</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="0.00E+00">
-                  <c:v>3.7072332230313697E-4</c:v>
+                  <c:v>3.2185131927681701E-4</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="0.00E+00">
-                  <c:v>3.6316677801223601E-4</c:v>
+                  <c:v>3.2322491950519903E-4</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="0.00E+00">
-                  <c:v>3.5427950006193803E-4</c:v>
+                  <c:v>3.1002704032439502E-4</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="0.00E+00">
-                  <c:v>3.5098998913497299E-4</c:v>
+                  <c:v>3.1055767779179902E-4</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="0.00E+00">
-                  <c:v>3.4879522474423499E-4</c:v>
+                  <c:v>3.1535592702067801E-4</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.00E+00">
-                  <c:v>3.6394457758151701E-4</c:v>
+                  <c:v>3.20436735596234E-4</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="0.00E+00">
-                  <c:v>3.5337792221981401E-4</c:v>
+                  <c:v>3.2646913317759397E-4</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="0.00E+00">
-                  <c:v>3.4898961428167502E-4</c:v>
+                  <c:v>3.15527392673664E-4</c:v>
                 </c:pt>
                 <c:pt idx="68" formatCode="0.00E+00">
-                  <c:v>3.4365049754743297E-4</c:v>
+                  <c:v>3.1288051432217499E-4</c:v>
                 </c:pt>
                 <c:pt idx="69" formatCode="0.00E+00">
-                  <c:v>3.45993353399636E-4</c:v>
+                  <c:v>3.0376232066447702E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1962,11 +1962,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="233034408"/>
-        <c:axId val="233027352"/>
+        <c:axId val="346527656"/>
+        <c:axId val="346525304"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="233034408"/>
+        <c:axId val="346527656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2079,12 +2079,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="233027352"/>
+        <c:crossAx val="346525304"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="233027352"/>
+        <c:axId val="346525304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2141,7 +2141,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="233034408"/>
+        <c:crossAx val="346527656"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2554,214 +2554,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>0.69443083399468597</c:v>
+                  <c:v>0.69501886122575696</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.70365265435138802</c:v>
+                  <c:v>0.70422313939555303</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.727148507956623</c:v>
+                  <c:v>0.727660346524444</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.74026436338123303</c:v>
+                  <c:v>0.74074246660453502</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.75675915673068905</c:v>
+                  <c:v>0.75719355402925304</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.77072946434079603</c:v>
+                  <c:v>0.77113276997658298</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.779178861176549</c:v>
+                  <c:v>0.77956346378253005</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.78969965170493095</c:v>
+                  <c:v>0.79005701441806897</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.79601985836070199</c:v>
+                  <c:v>0.79636193713272796</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.80071995968100296</c:v>
+                  <c:v>0.80105293934908495</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.80665864678321098</c:v>
+                  <c:v>0.80697447664993305</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.81078282218339504</c:v>
+                  <c:v>0.81108802514482004</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.81425283336104204</c:v>
+                  <c:v>0.814549954184842</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.81714927125713499</c:v>
+                  <c:v>0.81743933733791696</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.81943763050608898</c:v>
+                  <c:v>0.81971923531761204</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.82168382524391603</c:v>
+                  <c:v>0.82195772996990002</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.82357589559722</c:v>
+                  <c:v>0.823843278224617</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.82555883007989495</c:v>
+                  <c:v>0.82581609717512305</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.82698045114197005</c:v>
+                  <c:v>0.82722942299007196</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.82837648072457004</c:v>
+                  <c:v>0.82862076797168005</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.82927934498359901</c:v>
+                  <c:v>0.82952096402400599</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.83025231787179199</c:v>
+                  <c:v>0.83049028744769104</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.83081734323323597</c:v>
+                  <c:v>0.83105453178475397</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.83140633936759001</c:v>
+                  <c:v>0.83163926894149998</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.83190036732530004</c:v>
+                  <c:v>0.83213234967798799</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.83246526198460202</c:v>
+                  <c:v>0.83269471441885201</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.83285174821957497</c:v>
+                  <c:v>0.83307919626378002</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.83322563476802403</c:v>
+                  <c:v>0.83345208726547404</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.83352164898005199</c:v>
+                  <c:v>0.833747366607407</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.83376980006754597</c:v>
+                  <c:v>0.83399484677375102</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.83403661542096996</c:v>
+                  <c:v>0.83426007868198504</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.834272794192224</c:v>
+                  <c:v>0.83449570695006703</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.834525833539842</c:v>
+                  <c:v>0.83474830379495601</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.83470275195974697</c:v>
+                  <c:v>0.83492509025977601</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.83474235470888403</c:v>
+                  <c:v>0.83496479672950197</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.83497675593100096</c:v>
+                  <c:v>0.83519831045185999</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.83503578101849296</c:v>
+                  <c:v>0.83525694341110102</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.83517978863895104</c:v>
+                  <c:v>0.83540068030940196</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.83520203414358096</c:v>
+                  <c:v>0.83542206071617797</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.83525345236638804</c:v>
+                  <c:v>0.83547351466215503</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.83532939031110198</c:v>
+                  <c:v>0.83554906398719697</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.83530905305775005</c:v>
+                  <c:v>0.83552823179598001</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.83539970806369401</c:v>
+                  <c:v>0.83561842630808103</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.83544733592437204</c:v>
+                  <c:v>0.83566580779562505</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.83539808735712895</c:v>
+                  <c:v>0.83561717324394702</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.83545481208691597</c:v>
+                  <c:v>0.835673326180425</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.83548625902236895</c:v>
+                  <c:v>0.83570480941677605</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.83551341892755204</c:v>
+                  <c:v>0.83573159366262795</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.83555323080011601</c:v>
+                  <c:v>0.83577124792134905</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.83545076032050203</c:v>
+                  <c:v>0.83566875771743898</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.83550108064531303</c:v>
+                  <c:v>0.83571901081028799</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.83563133840039405</c:v>
+                  <c:v>0.83584896400312203</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.83570419177454802</c:v>
+                  <c:v>0.83592224214942201</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.83582833266936596</c:v>
+                  <c:v>0.83604613886561097</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.83576739933059496</c:v>
+                  <c:v>0.83598591347069995</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.83575882527005596</c:v>
+                  <c:v>0.83597659380620803</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.8356752281798</c:v>
+                  <c:v>0.83589287345879604</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.83571344548622695</c:v>
+                  <c:v>0.83593101359835598</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.83583382215934499</c:v>
+                  <c:v>0.83605107280563595</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.83578980167779704</c:v>
+                  <c:v>0.836006928400437</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.83579207589507398</c:v>
+                  <c:v>0.83600909515716804</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.83586126960924201</c:v>
+                  <c:v>0.836078274739532</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.83583800462790103</c:v>
+                  <c:v>0.83605511915856701</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.83585138852727903</c:v>
+                  <c:v>0.83606848517598997</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.83575856386577196</c:v>
+                  <c:v>0.83597607169615296</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.83590377394593895</c:v>
+                  <c:v>0.83612053954853105</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.83589099127641597</c:v>
+                  <c:v>0.83610842659524198</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.83594708863591904</c:v>
+                  <c:v>0.836163900788647</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.83595822445844803</c:v>
+                  <c:v>0.83617525668235604</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.83597796048194495</c:v>
+                  <c:v>0.83619478359843402</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2805,214 +2805,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>0.69636862395738897</c:v>
+                  <c:v>0.74620112723561005</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.72738753603457995</c:v>
+                  <c:v>0.76032454361054702</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.74627948509629605</c:v>
+                  <c:v>0.775828157917407</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.75956420768884103</c:v>
+                  <c:v>0.78945337687731199</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.77518677336143904</c:v>
+                  <c:v>0.79771866621765197</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.78640935597303496</c:v>
+                  <c:v>0.80505637483325099</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.79660414921792999</c:v>
+                  <c:v>0.81116780356131202</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.80312712717736701</c:v>
+                  <c:v>0.81711944050686403</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.80861766277383396</c:v>
+                  <c:v>0.82068109256750199</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.81200768424035297</c:v>
+                  <c:v>0.82286873370037605</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.81594275978096398</c:v>
+                  <c:v>0.82525937122285997</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.818907162791086</c:v>
+                  <c:v>0.82718828071769201</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.82152470845580094</c:v>
+                  <c:v>0.82827565322494301</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.82354635691304501</c:v>
+                  <c:v>0.82939944290857004</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.82556434571030302</c:v>
+                  <c:v>0.83029329532372098</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.82703769868032595</c:v>
+                  <c:v>0.83092055834449297</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.82804682378109695</c:v>
+                  <c:v>0.83140554637511999</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.82896921494019604</c:v>
+                  <c:v>0.83190437032221998</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.82988020887248004</c:v>
+                  <c:v>0.83222217871305004</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.83058461499854097</c:v>
+                  <c:v>0.83250868660604904</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.83126379561112596</c:v>
+                  <c:v>0.83273888492955395</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.83183608801168596</c:v>
+                  <c:v>0.83311715366482098</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.83214598279123297</c:v>
+                  <c:v>0.83333341164984098</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.83264688568163203</c:v>
+                  <c:v>0.83371992972398601</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.83313769836664098</c:v>
+                  <c:v>0.83405632523279505</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.83339152192711397</c:v>
+                  <c:v>0.83422543667979698</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.83358781040451801</c:v>
+                  <c:v>0.834378571559098</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.83374862632048397</c:v>
+                  <c:v>0.83444968294866795</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.83380208349671103</c:v>
+                  <c:v>0.834578826870916</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.83400352163852298</c:v>
+                  <c:v>0.83457261376125402</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.83415194699139295</c:v>
+                  <c:v>0.83465910129196097</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.83432944050072499</c:v>
+                  <c:v>0.83477302570608802</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.83447946041973098</c:v>
+                  <c:v>0.83501082073090105</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.83455667924544097</c:v>
+                  <c:v>0.83502724109214899</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.83459607287114901</c:v>
+                  <c:v>0.83514017349717096</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.83480532700107601</c:v>
+                  <c:v>0.83526621086458797</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.83499115930709</c:v>
+                  <c:v>0.83534567601504695</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.83512669742872303</c:v>
+                  <c:v>0.835218751060536</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.83518854568249001</c:v>
+                  <c:v>0.83531795197109604</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.83526234011206901</c:v>
+                  <c:v>0.83548139852399395</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.83530897463646503</c:v>
+                  <c:v>0.83550562443057297</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.83530573322333401</c:v>
+                  <c:v>0.83568549134472003</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.83533093259638203</c:v>
+                  <c:v>0.83569744766499299</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.83533561173307902</c:v>
+                  <c:v>0.83567752916637295</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.83543429185056395</c:v>
+                  <c:v>0.83567938265706998</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.83559889812865895</c:v>
+                  <c:v>0.835752608592365</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.83556721592934902</c:v>
+                  <c:v>0.83575816906445699</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.83549972134303196</c:v>
+                  <c:v>0.83575756863789297</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.83560190427793302</c:v>
+                  <c:v>0.83574368051041403</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.83558940915312296</c:v>
+                  <c:v>0.83579205400706402</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.83553488021932798</c:v>
+                  <c:v>0.83576641840333499</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.83561881713515496</c:v>
+                  <c:v>0.83585588196135796</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.83566296831884601</c:v>
+                  <c:v>0.83597455757699102</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.83563680174994404</c:v>
+                  <c:v>0.83601100085887103</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.83548484743923102</c:v>
+                  <c:v>0.83597513189805195</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.83552016315809796</c:v>
+                  <c:v>0.83590843233845202</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.835582769484291</c:v>
+                  <c:v>0.835877236262631</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.83560475358463704</c:v>
+                  <c:v>0.83594761669812401</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.83564150702706996</c:v>
+                  <c:v>0.83589480526600202</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.83568199855077396</c:v>
+                  <c:v>0.83590208870127702</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.83569363104144401</c:v>
+                  <c:v>0.83596463748593497</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.83571561514179005</c:v>
+                  <c:v>0.83596526401800197</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.83583578269148096</c:v>
+                  <c:v>0.83600823367557597</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.83588976267627701</c:v>
+                  <c:v>0.83599625124980004</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.835877555096181</c:v>
+                  <c:v>0.83593881914368695</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.83573213589258499</c:v>
+                  <c:v>0.83587671415257603</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.835710047230526</c:v>
+                  <c:v>0.83593208392397</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.83575080015851499</c:v>
+                  <c:v>0.83604475527396405</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.83579411484849497</c:v>
+                  <c:v>0.83601684849149305</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.83585214659970497</c:v>
+                  <c:v>0.83612398547489797</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3027,11 +3027,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="233033232"/>
-        <c:axId val="233026176"/>
+        <c:axId val="346530792"/>
+        <c:axId val="346523736"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="233033232"/>
+        <c:axId val="346530792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3144,12 +3144,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="233026176"/>
+        <c:crossAx val="346523736"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="233026176"/>
+        <c:axId val="346523736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0.65000000000000013"/>
@@ -3207,7 +3207,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="233033232"/>
+        <c:crossAx val="346530792"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3620,214 +3620,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>0.26692267867640501</c:v>
+                  <c:v>0.24248137726896299</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.25403799899908702</c:v>
+                  <c:v>0.23004055393266701</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.21216988915584101</c:v>
+                  <c:v>0.189787226376332</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.19266997775228401</c:v>
+                  <c:v>0.17223807650233</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.154116802701043</c:v>
+                  <c:v>0.136011819474154</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.14289300300110599</c:v>
+                  <c:v>0.12531785011733801</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.12481310405547801</c:v>
+                  <c:v>0.108573448887503</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.10708154494326701</c:v>
+                  <c:v>9.2017140764154098E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.9285162137684402E-2</c:v>
+                  <c:v>8.5021307464880999E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>9.3486067991894503E-2</c:v>
+                  <c:v>7.9633172787232698E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>8.3695020397505496E-2</c:v>
+                  <c:v>7.0574262899208595E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7.6165621867725394E-2</c:v>
+                  <c:v>6.3803051088916596E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7.3337319331953199E-2</c:v>
+                  <c:v>6.1118216980817E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>6.8877785950775094E-2</c:v>
+                  <c:v>5.7130168985491503E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>6.2276506883994699E-2</c:v>
+                  <c:v>5.1926189615518002E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5.1661968765753602E-2</c:v>
+                  <c:v>4.2730043039346202E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.8821097587909597E-2</c:v>
+                  <c:v>4.0386255013246303E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3.80017828620254E-2</c:v>
+                  <c:v>3.1356207532817301E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3.1337886635957601E-2</c:v>
+                  <c:v>2.6342982259605199E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2.5235854112321699E-2</c:v>
+                  <c:v>2.11680008709015E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2.38501221870107E-2</c:v>
+                  <c:v>2.0201696385246899E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2.0788834142309798E-2</c:v>
+                  <c:v>1.8066853195488598E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.9958825861053998E-2</c:v>
+                  <c:v>1.72020102657434E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.7209555556019201E-2</c:v>
+                  <c:v>1.5445119038144099E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.64519311431209E-2</c:v>
+                  <c:v>1.4671403373588E-2</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.42770552158487E-2</c:v>
+                  <c:v>1.28258802773508E-2</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.26642233332037E-2</c:v>
+                  <c:v>1.1641768169204101E-2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.21851419208609E-2</c:v>
+                  <c:v>1.13048966529794E-2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.19402811650997E-2</c:v>
+                  <c:v>1.11441615016592E-2</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.1500311220712E-2</c:v>
+                  <c:v>1.0939779823652299E-2</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.03342810766698E-2</c:v>
+                  <c:v>9.9838943432741592E-3</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.02580609014465E-2</c:v>
+                  <c:v>9.9584331293547899E-3</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1.0097684991696901E-2</c:v>
+                  <c:v>9.8335404521747195E-3</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1.0011447068847899E-2</c:v>
+                  <c:v>9.7849030792353693E-3</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>9.9403142157282499E-3</c:v>
+                  <c:v>9.6588041175554792E-3</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>9.2390872854716099E-3</c:v>
+                  <c:v>9.1182067013671209E-3</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>9.1335043510130196E-3</c:v>
+                  <c:v>9.1252426987026708E-3</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>9.0093052187663909E-3</c:v>
+                  <c:v>9.0231117517948004E-3</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>8.5206890569446605E-3</c:v>
+                  <c:v>8.8316953841792601E-3</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>8.3028261676686092E-3</c:v>
+                  <c:v>8.5955502032807503E-3</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>8.1898249803878699E-3</c:v>
+                  <c:v>8.5485810336897502E-3</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>8.0587852198404902E-3</c:v>
+                  <c:v>8.4828749146463097E-3</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>7.8837247689700907E-3</c:v>
+                  <c:v>8.3997347071112591E-3</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>7.8297850466704996E-3</c:v>
+                  <c:v>8.3957578879880704E-3</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>7.6367853810237196E-3</c:v>
+                  <c:v>7.9961705187613901E-3</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>7.4777400547704201E-3</c:v>
+                  <c:v>7.9205045917461192E-3</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>7.4554524753531904E-3</c:v>
+                  <c:v>7.8648687798054794E-3</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>7.4291705578077199E-3</c:v>
+                  <c:v>7.8912935688166298E-3</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>7.48158767878638E-3</c:v>
+                  <c:v>7.9154328743084104E-3</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>7.6424287520163899E-3</c:v>
+                  <c:v>8.0848900389158505E-3</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>7.6847223624788696E-3</c:v>
+                  <c:v>8.1020526939969799E-3</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>7.5203255638044099E-3</c:v>
+                  <c:v>7.9998175810887702E-3</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>7.28861227066014E-3</c:v>
+                  <c:v>7.72735885005794E-3</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>7.24450810327889E-3</c:v>
+                  <c:v>7.6890506909253198E-3</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>7.3643567891827104E-3</c:v>
+                  <c:v>7.8508997318125495E-3</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>7.4251359718250903E-3</c:v>
+                  <c:v>7.9772810610362396E-3</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>7.5204550743036298E-3</c:v>
+                  <c:v>8.0813481735217893E-3</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>7.5439761160470001E-3</c:v>
+                  <c:v>8.0724134760579193E-3</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>7.3308709942068503E-3</c:v>
+                  <c:v>7.9055746589497596E-3</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>7.34612270156849E-3</c:v>
+                  <c:v>7.9165328697383998E-3</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>7.4544914343737598E-3</c:v>
+                  <c:v>8.0204828834836601E-3</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>7.1630371376724001E-3</c:v>
+                  <c:v>7.6265958013140402E-3</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>7.3632637374624298E-3</c:v>
+                  <c:v>7.8505179595205893E-3</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>7.4009930800018201E-3</c:v>
+                  <c:v>7.9668849691686607E-3</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>7.4473096305478397E-3</c:v>
+                  <c:v>7.9923870511095594E-3</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>7.3042233038313302E-3</c:v>
+                  <c:v>7.8430296499875894E-3</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>7.2511637291851703E-3</c:v>
+                  <c:v>7.8378116175624908E-3</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>7.1772302582357502E-3</c:v>
+                  <c:v>7.71473891857518E-3</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>7.2046816608610301E-3</c:v>
+                  <c:v>7.7734293340226898E-3</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>7.3461647539781599E-3</c:v>
+                  <c:v>7.9331898255848906E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3871,214 +3871,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>0.234109042658696</c:v>
+                  <c:v>0.112178219518469</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.16807668836870199</c:v>
+                  <c:v>9.1656116116686795E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.156084854534493</c:v>
+                  <c:v>6.8421978091273802E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.14485280444220899</c:v>
+                  <c:v>5.6196211089671697E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.135395127061051</c:v>
+                  <c:v>5.0797121470985702E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.10271012935615501</c:v>
+                  <c:v>4.3063735614371899E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.76860482259577E-2</c:v>
+                  <c:v>3.9981009317382299E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.8142895613655302E-2</c:v>
+                  <c:v>3.2538260770773299E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.9257300058918903E-2</c:v>
+                  <c:v>3.0035721551089599E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.95883531661986E-2</c:v>
+                  <c:v>2.8965586295757701E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4.8807878090847301E-2</c:v>
+                  <c:v>2.3234866493898401E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4.3516922080397702E-2</c:v>
+                  <c:v>1.9756211494142899E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.6410822924478399E-2</c:v>
+                  <c:v>1.8278307958744099E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.5964746092669302E-2</c:v>
+                  <c:v>1.4980437357110099E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.16092764502134E-2</c:v>
+                  <c:v>1.3816162884028401E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.6169221569723299E-2</c:v>
+                  <c:v>1.3032464636151901E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.54623950742787E-2</c:v>
+                  <c:v>1.24627273504288E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2.4827873436180301E-2</c:v>
+                  <c:v>1.11809475974738E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2.21413654640846E-2</c:v>
+                  <c:v>1.10261351850261E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2.1014724820395798E-2</c:v>
+                  <c:v>1.0635982241785301E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.7896974561768399E-2</c:v>
+                  <c:v>1.04758374638396E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.7149501319780401E-2</c:v>
+                  <c:v>1.03730969487186E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.5332619965648501E-2</c:v>
+                  <c:v>1.0066406157444301E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.45897031831996E-2</c:v>
+                  <c:v>9.5061967776241506E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.24479952869033E-2</c:v>
+                  <c:v>8.7324075435115008E-3</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.13246803789808E-2</c:v>
+                  <c:v>8.4479202395479902E-3</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.0729618711685001E-2</c:v>
+                  <c:v>8.3473585235140802E-3</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.0251855562514799E-2</c:v>
+                  <c:v>8.2800714985148995E-3</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.0258081598604101E-2</c:v>
+                  <c:v>8.0331553662165208E-3</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>9.6158464703729792E-3</c:v>
+                  <c:v>8.0180870732983207E-3</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>9.5523033520374598E-3</c:v>
+                  <c:v>8.1060164032116903E-3</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>8.7211348089341299E-3</c:v>
+                  <c:v>7.98294476008439E-3</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>8.6563172782411404E-3</c:v>
+                  <c:v>7.6825102723703E-3</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>8.0988837236738494E-3</c:v>
+                  <c:v>7.7027839226647904E-3</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>8.2032448724222596E-3</c:v>
+                  <c:v>7.5885399988517297E-3</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>7.8069959868625298E-3</c:v>
+                  <c:v>7.4967387326986103E-3</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>7.54934772437165E-3</c:v>
+                  <c:v>7.3873908810105204E-3</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>7.4988519453889997E-3</c:v>
+                  <c:v>7.7056685704100904E-3</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>7.5657005777816904E-3</c:v>
+                  <c:v>7.6223554587906998E-3</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>7.5058346124321097E-3</c:v>
+                  <c:v>7.4501702088706203E-3</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>7.5228260207036097E-3</c:v>
+                  <c:v>7.1867459255916099E-3</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>7.5351286662872601E-3</c:v>
+                  <c:v>7.0336575306717301E-3</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>7.4440450941545997E-3</c:v>
+                  <c:v>7.0479932250102403E-3</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>7.2054063399408803E-3</c:v>
+                  <c:v>7.2644465288397098E-3</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>7.0885347152659E-3</c:v>
+                  <c:v>7.16653461983798E-3</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>6.8325836493460801E-3</c:v>
+                  <c:v>7.0961338047883498E-3</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>6.9013491485816402E-3</c:v>
+                  <c:v>7.0768978913993402E-3</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>7.0304840689678601E-3</c:v>
+                  <c:v>7.0998361946441801E-3</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>6.8167828213080697E-3</c:v>
+                  <c:v>7.1727181135409403E-3</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>6.8941721498653403E-3</c:v>
+                  <c:v>7.0731563384426798E-3</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>6.8152108553856004E-3</c:v>
+                  <c:v>7.2057541422606598E-3</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>6.7567921983850898E-3</c:v>
+                  <c:v>7.0195338789596998E-3</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>6.6934885390288199E-3</c:v>
+                  <c:v>6.9044677173707202E-3</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>6.7002705054229504E-3</c:v>
+                  <c:v>6.9053820821742403E-3</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>6.9144437437235499E-3</c:v>
+                  <c:v>6.98845962606311E-3</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>6.8885802080286803E-3</c:v>
+                  <c:v>7.1478716323320601E-3</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>6.6920275220475802E-3</c:v>
+                  <c:v>7.08605930925023E-3</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>6.6997672563816699E-3</c:v>
+                  <c:v>7.0580925189797396E-3</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>6.67972880720421E-3</c:v>
+                  <c:v>7.06873024478672E-3</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>6.70085043252403E-3</c:v>
+                  <c:v>7.1408693089871503E-3</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>6.8043968461183602E-3</c:v>
+                  <c:v>7.1574243929256598E-3</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>6.7120767264596797E-3</c:v>
+                  <c:v>7.1588509762967999E-3</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>6.5800666315721E-3</c:v>
+                  <c:v>7.03841821743345E-3</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>6.6161681612734802E-3</c:v>
+                  <c:v>7.1353013202611502E-3</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>6.5501295176829703E-3</c:v>
+                  <c:v>7.3076983688676904E-3</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>6.7681040598583297E-3</c:v>
+                  <c:v>7.4165157683646898E-3</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>6.8312880413683996E-3</c:v>
+                  <c:v>7.4319779104611598E-3</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>6.7715277611400098E-3</c:v>
+                  <c:v>7.24751559154105E-3</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>6.7235627618723003E-3</c:v>
+                  <c:v>7.2610096244785797E-3</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>6.6769066942950197E-3</c:v>
+                  <c:v>7.0695668347329904E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4093,11 +4093,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="233035192"/>
-        <c:axId val="233024216"/>
+        <c:axId val="346531576"/>
+        <c:axId val="346525696"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="233035192"/>
+        <c:axId val="346531576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4210,12 +4210,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="233024216"/>
+        <c:crossAx val="346525696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="233024216"/>
+        <c:axId val="346525696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4272,7 +4272,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="233035192"/>
+        <c:crossAx val="346531576"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4685,214 +4685,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>0.77155569002671098</c:v>
+                  <c:v>0.77178122555217299</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.79372142051421202</c:v>
+                  <c:v>0.79393219793924297</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.79984229178230204</c:v>
+                  <c:v>0.80006596616597603</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.83413450849187998</c:v>
+                  <c:v>0.83428731992295901</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.83212896486716104</c:v>
+                  <c:v>0.83223977300482699</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.828178909382151</c:v>
+                  <c:v>0.82830132842175697</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.81786258915147003</c:v>
+                  <c:v>0.81807064960546005</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.82412997501646701</c:v>
+                  <c:v>0.824403345933584</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.83309965084534299</c:v>
+                  <c:v>0.83336065872968401</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.84630228569939203</c:v>
+                  <c:v>0.84652181328391796</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.81934712199704096</c:v>
+                  <c:v>0.81964353153660996</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.79627680291540504</c:v>
+                  <c:v>0.79662606808636205</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.75603794320373396</c:v>
+                  <c:v>0.75639660763948102</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.72587809206409604</c:v>
+                  <c:v>0.72622632080295801</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.69049950945625904</c:v>
+                  <c:v>0.69088788029685499</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.65978415609247898</c:v>
+                  <c:v>0.66019943349735799</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.614684031765098</c:v>
+                  <c:v>0.61507992033238601</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.60175523923192697</c:v>
+                  <c:v>0.60210579766070005</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.57404522530574398</c:v>
+                  <c:v>0.57446704068642596</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.559672838670213</c:v>
+                  <c:v>0.56011853004919498</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.53736228271698605</c:v>
+                  <c:v>0.53781197847073303</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.52606070980841402</c:v>
+                  <c:v>0.52649596192260395</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.49839057703582801</c:v>
+                  <c:v>0.49884128563318197</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.49674980397642499</c:v>
+                  <c:v>0.49719740709377303</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.49302189206452601</c:v>
+                  <c:v>0.49348048858460197</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.49056595631507799</c:v>
+                  <c:v>0.49100768337885198</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.47642252149867398</c:v>
+                  <c:v>0.47685951082876299</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.47969611189959699</c:v>
+                  <c:v>0.480107240085551</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.47278711190129602</c:v>
+                  <c:v>0.47319353462423303</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.461229445176496</c:v>
+                  <c:v>0.46170513841057698</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.46392120477802001</c:v>
+                  <c:v>0.464350482353028</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.45530688919616502</c:v>
+                  <c:v>0.45572799216972898</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.44504607446079097</c:v>
+                  <c:v>0.44545517737214102</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.44116830619323999</c:v>
+                  <c:v>0.44152762477581903</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.45663593545159198</c:v>
+                  <c:v>0.45699015000113002</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.44270502297917702</c:v>
+                  <c:v>0.44306527457008599</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.44338868934126002</c:v>
+                  <c:v>0.44379483308733902</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.43121230545956202</c:v>
+                  <c:v>0.43162842811778701</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.436219893068164</c:v>
+                  <c:v>0.43664144398022497</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.43428562870499199</c:v>
+                  <c:v>0.434722198627564</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.43514931399264301</c:v>
+                  <c:v>0.435601053644738</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.442056120019932</c:v>
+                  <c:v>0.44248234587130503</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.43322661058707701</c:v>
+                  <c:v>0.43366561847336699</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.43138005773309701</c:v>
+                  <c:v>0.43179942584511</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.43438401107605001</c:v>
+                  <c:v>0.43481588718970998</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.43825126033443701</c:v>
+                  <c:v>0.43870323887586998</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.449400976562289</c:v>
+                  <c:v>0.44983228002756298</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.44744150935195398</c:v>
+                  <c:v>0.4478985976582</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.45340426252174398</c:v>
+                  <c:v>0.45383955760938799</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.47172911767634601</c:v>
+                  <c:v>0.47215523970996898</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.46483759642641298</c:v>
+                  <c:v>0.46527833834614202</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.44658852808927602</c:v>
+                  <c:v>0.447043945111954</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.423152864070791</c:v>
+                  <c:v>0.42366191650947399</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.41541129337730798</c:v>
+                  <c:v>0.41593347807768799</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.42413575012392601</c:v>
+                  <c:v>0.42470349988948097</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.42343393647435501</c:v>
+                  <c:v>0.42399948738135801</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.43992861489573198</c:v>
+                  <c:v>0.44044625494893203</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.44746590871184799</c:v>
+                  <c:v>0.44796517200416702</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.43005095565944301</c:v>
+                  <c:v>0.43060952007012399</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.42694431354073897</c:v>
+                  <c:v>0.42748019738957599</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.43844910447376401</c:v>
+                  <c:v>0.43898692697111003</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.41960948354176902</c:v>
+                  <c:v>0.42017298195222402</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.43988316818477402</c:v>
+                  <c:v>0.44038777393823397</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.44847176966455099</c:v>
+                  <c:v>0.448908825196151</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.45234610874147402</c:v>
+                  <c:v>0.45286047931475798</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.438113785044422</c:v>
+                  <c:v>0.43861672505837601</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.44462901163156299</c:v>
+                  <c:v>0.44511319199681099</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.44136244756225601</c:v>
+                  <c:v>0.44185253035361</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.43513166612583698</c:v>
+                  <c:v>0.435651257977615</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.43934148832626801</c:v>
+                  <c:v>0.43988995023731098</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4936,214 +4936,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>0.69411711188485103</c:v>
+                  <c:v>0.65396779990576803</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.75857739221243103</c:v>
+                  <c:v>0.76069737293129402</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.77127695107928296</c:v>
+                  <c:v>0.80975809452680403</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.80406520669412396</c:v>
+                  <c:v>0.79576459941422295</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.79646248774501405</c:v>
+                  <c:v>0.79627198066660998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.79904692418152701</c:v>
+                  <c:v>0.810361624910233</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.80030632985618799</c:v>
+                  <c:v>0.80688383600059899</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.81809960410622795</c:v>
+                  <c:v>0.78976111820765604</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.81544775870104802</c:v>
+                  <c:v>0.774079805845171</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.80563780700709098</c:v>
+                  <c:v>0.730582759530225</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.77834476945300302</c:v>
+                  <c:v>0.67512694541234297</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.726435315594398</c:v>
+                  <c:v>0.61874202576439097</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.71281340240402002</c:v>
+                  <c:v>0.56050129904967905</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.67850844524521703</c:v>
+                  <c:v>0.53640921922487095</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.63408843291719097</c:v>
+                  <c:v>0.51703931902566302</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.58803624309374802</c:v>
+                  <c:v>0.500245711080616</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.55718182818927098</c:v>
+                  <c:v>0.484643383715056</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.53615822511116396</c:v>
+                  <c:v>0.46791157784166798</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.53313269679365705</c:v>
+                  <c:v>0.47592419269982</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.50687074119832498</c:v>
+                  <c:v>0.45627693797462998</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.49867072951340302</c:v>
+                  <c:v>0.45921434713395298</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.49320149064164898</c:v>
+                  <c:v>0.45575766435808401</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.473647399762957</c:v>
+                  <c:v>0.44347750227716098</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.45038720937019899</c:v>
+                  <c:v>0.42496433140641499</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.45082879836748602</c:v>
+                  <c:v>0.433224168039338</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.43486008618920202</c:v>
+                  <c:v>0.446257153365613</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.433947046222808</c:v>
+                  <c:v>0.44166406434991601</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.42518474214597402</c:v>
+                  <c:v>0.438585237253306</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.42733963280660903</c:v>
+                  <c:v>0.43296303442863099</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.41810427574568199</c:v>
+                  <c:v>0.45270000392256599</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.436609156212585</c:v>
+                  <c:v>0.45960422821835101</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.43651855719183602</c:v>
+                  <c:v>0.44448562327177699</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.436463127747659</c:v>
+                  <c:v>0.43245412942459899</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.42919533274959998</c:v>
+                  <c:v>0.44449669170394501</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.43498570366974698</c:v>
+                  <c:v>0.43725398447184899</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.423854802030671</c:v>
+                  <c:v>0.42639494007614398</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.41374048080776898</c:v>
+                  <c:v>0.42637078851808502</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.419172535140034</c:v>
+                  <c:v>0.45067180975557303</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.417197497891661</c:v>
+                  <c:v>0.43494374478353498</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.42286756274987403</c:v>
+                  <c:v>0.42750802187060599</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.43086344738056398</c:v>
+                  <c:v>0.433094664618769</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.42490235137765803</c:v>
+                  <c:v>0.42593593971446703</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.43602749389336498</c:v>
+                  <c:v>0.42209466948455898</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.43179844839018799</c:v>
+                  <c:v>0.43599641679122503</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.42829952941053501</c:v>
+                  <c:v>0.43220452521299002</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.41867300035092297</c:v>
+                  <c:v>0.43313261793802199</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.44348014084576298</c:v>
+                  <c:v>0.427436882528828</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.44637596730389001</c:v>
+                  <c:v>0.433993100223518</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.42827045781535</c:v>
+                  <c:v>0.43868890221316398</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.441772369366146</c:v>
+                  <c:v>0.43132629596622901</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.430533553846915</c:v>
+                  <c:v>0.43977625690838401</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.42570471559617501</c:v>
+                  <c:v>0.43503031676729098</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.40993580891717701</c:v>
+                  <c:v>0.41925587004107301</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.41443535009536597</c:v>
+                  <c:v>0.41439062357508799</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.44405364220156901</c:v>
+                  <c:v>0.41821733749786</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.42905659708647198</c:v>
+                  <c:v>0.432874380402967</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.40745946475342598</c:v>
+                  <c:v>0.41124166178965998</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.41577650028864299</c:v>
+                  <c:v>0.41441029043151201</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.413374471993948</c:v>
+                  <c:v>0.42458987376603802</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.40597795616978799</c:v>
+                  <c:v>0.434830710163643</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.40695264531613801</c:v>
+                  <c:v>0.442058648947251</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.42628385854080703</c:v>
+                  <c:v>0.41953899809209799</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.414625101227799</c:v>
+                  <c:v>0.41532718042779199</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.41606518548181398</c:v>
+                  <c:v>0.42907932117533698</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.40948921822852802</c:v>
+                  <c:v>0.43001316148949098</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.41464277163319901</c:v>
+                  <c:v>0.44113709240117599</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.42351543952509602</c:v>
+                  <c:v>0.43980577711858498</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.42800885054617199</c:v>
+                  <c:v>0.43948930173637002</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.42683558779909198</c:v>
+                  <c:v>0.44706616000657301</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.42118228405132702</c:v>
+                  <c:v>0.42858392088623698</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5158,11 +5158,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="233039112"/>
-        <c:axId val="233037936"/>
+        <c:axId val="346522560"/>
+        <c:axId val="346526872"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="233039112"/>
+        <c:axId val="346522560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5275,12 +5275,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="233037936"/>
+        <c:crossAx val="346526872"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="233037936"/>
+        <c:axId val="346526872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5337,7 +5337,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="233039112"/>
+        <c:crossAx val="346522560"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -8238,8 +8238,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="6157914" cy="1171576"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2"/>
@@ -8864,7 +8864,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2"/>
@@ -9379,7 +9379,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>717.8</v>
+        <v>387.4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -9393,7 +9393,7 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>581.6</v>
+        <v>311.7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -9407,7 +9407,7 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>482.1</v>
+        <v>244.7</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -9421,7 +9421,7 @@
         <v>4</v>
       </c>
       <c r="D5">
-        <v>453.3</v>
+        <v>196.9</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -9435,7 +9435,7 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>390</v>
+        <v>184.2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -9449,7 +9449,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>337.5</v>
+        <v>167.2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -9463,7 +9463,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>282.8</v>
+        <v>152.80000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -9477,7 +9477,7 @@
         <v>8</v>
       </c>
       <c r="D9">
-        <v>239.1</v>
+        <v>126.1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -9491,7 +9491,7 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>214</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -9505,7 +9505,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>208.8</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -9519,7 +9519,7 @@
         <v>11</v>
       </c>
       <c r="D12">
-        <v>177</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -9533,7 +9533,7 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>159.69999999999999</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -9547,7 +9547,7 @@
         <v>13</v>
       </c>
       <c r="D14">
-        <v>134.80000000000001</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -9561,7 +9561,7 @@
         <v>14</v>
       </c>
       <c r="D15">
-        <v>130</v>
+        <v>67.400000000000006</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -9575,7 +9575,7 @@
         <v>15</v>
       </c>
       <c r="D16">
-        <v>116.8</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -9589,7 +9589,7 @@
         <v>16</v>
       </c>
       <c r="D17">
-        <v>100</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -9603,7 +9603,7 @@
         <v>17</v>
       </c>
       <c r="D18">
-        <v>98</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -9617,7 +9617,7 @@
         <v>18</v>
       </c>
       <c r="D19">
-        <v>93.2</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -9631,7 +9631,7 @@
         <v>19</v>
       </c>
       <c r="D20">
-        <v>83.9</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -9645,7 +9645,7 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>76</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -9659,7 +9659,7 @@
         <v>21</v>
       </c>
       <c r="D22">
-        <v>68.5</v>
+        <v>40.200000000000003</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -9673,7 +9673,7 @@
         <v>22</v>
       </c>
       <c r="D23">
-        <v>66.7</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -9687,7 +9687,7 @@
         <v>23</v>
       </c>
       <c r="D24">
-        <v>59.5</v>
+        <v>37.700000000000003</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -9701,7 +9701,7 @@
         <v>24</v>
       </c>
       <c r="D25">
-        <v>56</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -9715,7 +9715,7 @@
         <v>25</v>
       </c>
       <c r="D26">
-        <v>49.5</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -9729,7 +9729,7 @@
         <v>26</v>
       </c>
       <c r="D27">
-        <v>42.6</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -9743,7 +9743,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>37.1</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -9757,7 +9757,7 @@
         <v>28</v>
       </c>
       <c r="D29">
-        <v>33.5</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -9771,7 +9771,7 @@
         <v>29</v>
       </c>
       <c r="D30">
-        <v>33.5</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -9785,7 +9785,7 @@
         <v>30</v>
       </c>
       <c r="D31">
-        <v>31.6</v>
+        <v>20.399999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -9799,7 +9799,7 @@
         <v>31</v>
       </c>
       <c r="D32">
-        <v>31.2</v>
+        <v>20.100000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -9813,7 +9813,7 @@
         <v>32</v>
       </c>
       <c r="D33">
-        <v>25.3</v>
+        <v>17.399999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -9827,7 +9827,7 @@
         <v>33</v>
       </c>
       <c r="D34">
-        <v>24.7</v>
+        <v>17.399999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -9841,7 +9841,7 @@
         <v>34</v>
       </c>
       <c r="D35">
-        <v>21.6</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -9855,7 +9855,7 @@
         <v>35</v>
       </c>
       <c r="D36">
-        <v>21.6</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -9869,7 +9869,7 @@
         <v>36</v>
       </c>
       <c r="D37">
-        <v>18.899999999999999</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -9883,7 +9883,7 @@
         <v>37</v>
       </c>
       <c r="D38">
-        <v>18.2</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -9897,7 +9897,7 @@
         <v>38</v>
       </c>
       <c r="D39">
-        <v>17.7</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -9911,7 +9911,7 @@
         <v>39</v>
       </c>
       <c r="D40">
-        <v>17.600000000000001</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -9925,7 +9925,7 @@
         <v>40</v>
       </c>
       <c r="D41">
-        <v>16.5</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -9939,7 +9939,7 @@
         <v>41</v>
       </c>
       <c r="D42">
-        <v>16.5</v>
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -9953,7 +9953,7 @@
         <v>42</v>
       </c>
       <c r="D43">
-        <v>16.399999999999999</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -9967,7 +9967,7 @@
         <v>43</v>
       </c>
       <c r="D44">
-        <v>14.3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -9981,7 +9981,7 @@
         <v>44</v>
       </c>
       <c r="D45">
-        <v>12.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -9995,7 +9995,7 @@
         <v>45</v>
       </c>
       <c r="D46">
-        <v>12.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -10009,7 +10009,7 @@
         <v>46</v>
       </c>
       <c r="D47">
-        <v>11.6</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -10023,7 +10023,7 @@
         <v>47</v>
       </c>
       <c r="D48">
-        <v>10.5</v>
+        <v>8.1999999999999993</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -10037,7 +10037,7 @@
         <v>48</v>
       </c>
       <c r="D49">
-        <v>10.1</v>
+        <v>8.1999999999999993</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -10051,7 +10051,7 @@
         <v>49</v>
       </c>
       <c r="D50">
-        <v>9.3000000000000007</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -10065,7 +10065,7 @@
         <v>50</v>
       </c>
       <c r="D51">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -10079,7 +10079,7 @@
         <v>51</v>
       </c>
       <c r="D52">
-        <v>8.1</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -10093,7 +10093,7 @@
         <v>52</v>
       </c>
       <c r="D53">
-        <v>7</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -10101,13 +10101,13 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>7.9052999999999898</v>
+        <v>7.90519999999999</v>
       </c>
       <c r="C54">
         <v>53</v>
       </c>
       <c r="D54">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -10115,13 +10115,13 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>7.6043000000000003</v>
+        <v>7.6048</v>
       </c>
       <c r="C55">
         <v>54</v>
       </c>
       <c r="D55">
-        <v>6.3</v>
+        <v>5.2039</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -10129,13 +10129,13 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>6.7077999999999998</v>
+        <v>6.7077</v>
       </c>
       <c r="C56">
         <v>55</v>
       </c>
       <c r="D56">
-        <v>5.8</v>
+        <v>5.1048</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -10143,13 +10143,13 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>6.7045999999999903</v>
+        <v>6.7045000000000003</v>
       </c>
       <c r="C57">
         <v>56</v>
       </c>
       <c r="D57">
-        <v>5.4</v>
+        <v>4.3048000000000002</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -10157,13 +10157,13 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>6.6041999999999996</v>
+        <v>6.6044999999999998</v>
       </c>
       <c r="C58">
         <v>57</v>
       </c>
       <c r="D58">
-        <v>5.0999999999999996</v>
+        <v>4.3051000000000004</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -10171,13 +10171,13 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>6.5042</v>
+        <v>6.5045000000000002</v>
       </c>
       <c r="C59">
         <v>58</v>
       </c>
       <c r="D59">
-        <v>5</v>
+        <v>4.1054000000000004</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -10185,13 +10185,13 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>5.9040999999999997</v>
+        <v>5.9042000000000003</v>
       </c>
       <c r="C60">
         <v>59</v>
       </c>
       <c r="D60">
-        <v>5</v>
+        <v>4.1051000000000002</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -10205,7 +10205,7 @@
         <v>60</v>
       </c>
       <c r="D61">
-        <v>4.9000000000000004</v>
+        <v>4.0050999999999997</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -10219,7 +10219,7 @@
         <v>61</v>
       </c>
       <c r="D62">
-        <v>4.5</v>
+        <v>3.9045000000000001</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -10227,13 +10227,13 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>4.8040000000000003</v>
+        <v>4.8037000000000001</v>
       </c>
       <c r="C63">
         <v>62</v>
       </c>
       <c r="D63">
-        <v>3.8</v>
+        <v>3.7058</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -10241,13 +10241,13 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>4.7052999999999896</v>
+        <v>4.7051999999999996</v>
       </c>
       <c r="C64">
         <v>63</v>
       </c>
       <c r="D64">
-        <v>3.4039000000000001</v>
+        <v>3.7058</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -10255,13 +10255,13 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>4.7052999999999896</v>
+        <v>4.7051999999999996</v>
       </c>
       <c r="C65">
         <v>64</v>
       </c>
       <c r="D65">
-        <v>2.9037999999999999</v>
+        <v>3.5093000000000001</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -10269,13 +10269,13 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>4.7039</v>
+        <v>4.7039999999999997</v>
       </c>
       <c r="C66">
         <v>65</v>
       </c>
       <c r="D66">
-        <v>2.7042999999999999</v>
+        <v>3.4152999999999998</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -10283,13 +10283,13 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>4.7036999999999898</v>
+        <v>4.7039</v>
       </c>
       <c r="C67">
         <v>66</v>
       </c>
       <c r="D67">
-        <v>2.6067</v>
+        <v>3.2141999999999902</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -10297,13 +10297,13 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>4.6044999999999998</v>
+        <v>4.6045999999999996</v>
       </c>
       <c r="C68">
         <v>67</v>
       </c>
       <c r="D68">
-        <v>2.6067</v>
+        <v>3.0137</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -10317,7 +10317,7 @@
         <v>68</v>
       </c>
       <c r="D69">
-        <v>2.5050999999999899</v>
+        <v>2.9127999999999998</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -10331,7 +10331,7 @@
         <v>69</v>
       </c>
       <c r="D70">
-        <v>2.2050999999999998</v>
+        <v>2.8128000000000002</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -10345,7 +10345,7 @@
         <v>70</v>
       </c>
       <c r="D71">
-        <v>2.1042000000000001</v>
+        <v>2.7111000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -10378,13 +10378,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>8.6474210885704103E-3</v>
+        <v>8.6238154451302295E-3</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>1.40112913580365E-2</v>
+        <v>1.1159649179412401E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -10392,13 +10392,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>6.97459970716292E-3</v>
+        <v>6.9493374459024902E-3</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>8.8266292191054602E-3</v>
+        <v>7.9365973298077108E-3</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -10406,13 +10406,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>5.8356701598041702E-3</v>
+        <v>5.8135592505184604E-3</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4">
-        <v>7.0964271569460497E-3</v>
+        <v>5.5631305807959898E-3</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -10420,13 +10420,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>4.6643627179502496E-3</v>
+        <v>4.6438771725312803E-3</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>5.07279307842205E-3</v>
+        <v>4.2111813759793497E-3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -10434,13 +10434,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>4.1485347585777897E-3</v>
+        <v>4.1269211164086097E-3</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6">
-        <v>3.95987884099731E-3</v>
+        <v>3.0404625080717499E-3</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -10448,13 +10448,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>3.3519807553477401E-3</v>
+        <v>3.3344745739752901E-3</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7">
-        <v>3.1673688946447101E-3</v>
+        <v>2.3215111549507502E-3</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -10462,13 +10462,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2.9944450997469998E-3</v>
+        <v>2.9808691587765298E-3</v>
       </c>
       <c r="C8">
         <v>7</v>
       </c>
       <c r="D8">
-        <v>2.5228099155473302E-3</v>
+        <v>1.8586010019362199E-3</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -10476,13 +10476,13 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>2.4400331965300699E-3</v>
+        <v>2.4289087630244201E-3</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
       <c r="D9">
-        <v>2.1714629111952701E-3</v>
+        <v>1.4185622928898601E-3</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -10490,13 +10490,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>2.0743917265516202E-3</v>
+        <v>2.06211627272612E-3</v>
       </c>
       <c r="C10">
         <v>9</v>
       </c>
       <c r="D10">
-        <v>1.75806982359715E-3</v>
+        <v>1.1626559016751001E-3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -10504,13 +10504,13 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1.78275308947511E-3</v>
+        <v>1.7727286221109299E-3</v>
       </c>
       <c r="C11">
         <v>10</v>
       </c>
       <c r="D11">
-        <v>1.4952954162514201E-3</v>
+        <v>1.0298255071569699E-3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -10518,13 +10518,13 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>1.59281646378411E-3</v>
+        <v>1.58167746719226E-3</v>
       </c>
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12">
-        <v>1.30525868999047E-3</v>
+      <c r="D12" s="1">
+        <v>9.1545133228479502E-4</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -10532,13 +10532,13 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1.37175510700166E-3</v>
+        <v>1.3602928802401301E-3</v>
       </c>
       <c r="C13">
         <v>12</v>
       </c>
-      <c r="D13">
-        <v>1.1814921525444299E-3</v>
+      <c r="D13" s="1">
+        <v>8.0900468996901497E-4</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -10546,13 +10546,13 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1.1863949707377501E-3</v>
+        <v>1.17601729199454E-3</v>
       </c>
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="D14">
-        <v>1.0537908140483001E-3</v>
+      <c r="D14" s="1">
+        <v>7.5551518540957995E-4</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -10560,13 +10560,13 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>1.0461775114207401E-3</v>
+        <v>1.03768341005777E-3</v>
       </c>
       <c r="C15">
         <v>14</v>
       </c>
       <c r="D15" s="1">
-        <v>9.0883116938525303E-4</v>
+        <v>6.7220636025611298E-4</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -10574,13 +10574,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>9.2253163283763796E-4</v>
+        <v>9.1338433016364203E-4</v>
       </c>
       <c r="C16">
         <v>15</v>
       </c>
       <c r="D16" s="1">
-        <v>8.3438221475302097E-4</v>
+        <v>6.2925969887452798E-4</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -10588,13 +10588,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>8.47669526110021E-4</v>
+        <v>8.3714619276021305E-4</v>
       </c>
       <c r="C17">
         <v>16</v>
       </c>
       <c r="D17" s="1">
-        <v>7.80675983803895E-4</v>
+        <v>5.9935016274222802E-4</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -10602,13 +10602,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>7.9150650370939601E-4</v>
+        <v>7.8464288313204601E-4</v>
       </c>
       <c r="C18">
         <v>17</v>
       </c>
       <c r="D18" s="1">
-        <v>7.2276514432390395E-4</v>
+        <v>5.5349477484964698E-4</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -10616,13 +10616,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>7.48181500298473E-4</v>
+        <v>7.3980277889194499E-4</v>
       </c>
       <c r="C19">
         <v>18</v>
       </c>
       <c r="D19" s="1">
-        <v>6.9008205560913997E-4</v>
+        <v>5.3927534346311502E-4</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -10630,13 +10630,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>7.1114687764625695E-4</v>
+        <v>7.0377031857641302E-4</v>
       </c>
       <c r="C20">
         <v>19</v>
       </c>
       <c r="D20" s="1">
-        <v>6.5433151134782397E-4</v>
+        <v>5.1743336242093103E-4</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -10644,13 +10644,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>6.6228085214212803E-4</v>
+        <v>6.5534414879862195E-4</v>
       </c>
       <c r="C21">
         <v>20</v>
       </c>
       <c r="D21" s="1">
-        <v>6.1155745660518095E-4</v>
+        <v>5.05424955588505E-4</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -10658,13 +10658,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
-        <v>6.2125290056156996E-4</v>
+        <v>6.1391868205965005E-4</v>
       </c>
       <c r="C22">
         <v>21</v>
       </c>
       <c r="D22" s="1">
-        <v>5.7418792124796895E-4</v>
+        <v>4.8916484149419696E-4</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -10672,13 +10672,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="1">
-        <v>5.6890341188297103E-4</v>
+        <v>5.5993713950838796E-4</v>
       </c>
       <c r="C23">
         <v>22</v>
       </c>
       <c r="D23" s="1">
-        <v>5.3080696486497198E-4</v>
+        <v>4.7137771584760302E-4</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -10686,13 +10686,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <v>5.4779069296664602E-4</v>
+        <v>5.4108139995146095E-4</v>
       </c>
       <c r="C24">
         <v>23</v>
       </c>
       <c r="D24" s="1">
-        <v>5.1688082885305395E-4</v>
+        <v>4.57792145933761E-4</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -10700,13 +10700,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <v>5.1802121603684295E-4</v>
+        <v>5.1169062633122297E-4</v>
       </c>
       <c r="C25">
         <v>24</v>
       </c>
       <c r="D25" s="1">
-        <v>4.9627885904685997E-4</v>
+        <v>4.4125051882311399E-4</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -10714,13 +10714,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="1">
-        <v>4.8499376756276001E-4</v>
+        <v>4.77852625756747E-4</v>
       </c>
       <c r="C26">
         <v>25</v>
       </c>
       <c r="D26" s="1">
-        <v>4.7774379937558898E-4</v>
+        <v>4.1686210379794701E-4</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -10728,13 +10728,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>4.6879331197938098E-4</v>
+        <v>4.6215836511428798E-4</v>
       </c>
       <c r="C27">
         <v>26</v>
       </c>
       <c r="D27" s="1">
-        <v>4.6897708181837801E-4</v>
+        <v>4.0386111111341902E-4</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -10742,13 +10742,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <v>4.57283968382422E-4</v>
+        <v>4.5274404144553699E-4</v>
       </c>
       <c r="C28">
         <v>27</v>
       </c>
       <c r="D28" s="1">
-        <v>4.6344539457096601E-4</v>
+        <v>3.9405328869416E-4</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -10756,13 +10756,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="1">
-        <v>4.24900547165198E-4</v>
+        <v>4.2232676484324402E-4</v>
       </c>
       <c r="C29">
         <v>28</v>
       </c>
       <c r="D29" s="1">
-        <v>4.5712133385636899E-4</v>
+        <v>3.9126379285902099E-4</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -10770,13 +10770,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="1">
-        <v>4.20908913669575E-4</v>
+        <v>4.1568668910077602E-4</v>
       </c>
       <c r="C30">
         <v>29</v>
       </c>
       <c r="D30" s="1">
-        <v>4.4714806172369302E-4</v>
+        <v>3.8610311717891002E-4</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -10784,13 +10784,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="1">
-        <v>4.05614331960135E-4</v>
+        <v>4.0237079682418599E-4</v>
       </c>
       <c r="C31">
         <v>30</v>
       </c>
       <c r="D31" s="1">
-        <v>4.3424867606708999E-4</v>
+        <v>3.8418442587055099E-4</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -10798,13 +10798,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="1">
-        <v>3.8480583313421402E-4</v>
+        <v>3.81095776479886E-4</v>
       </c>
       <c r="C32">
         <v>31</v>
       </c>
       <c r="D32" s="1">
-        <v>4.1990890500149299E-4</v>
+        <v>3.7306746478879999E-4</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -10812,13 +10812,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="1">
-        <v>3.68814584498239E-4</v>
+        <v>3.6681549408278699E-4</v>
       </c>
       <c r="C33">
         <v>32</v>
       </c>
       <c r="D33" s="1">
-        <v>4.08127887148878E-4</v>
+        <v>3.7533156528957699E-4</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -10826,13 +10826,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="1">
-        <v>3.5787141233278999E-4</v>
+        <v>3.5414776590699399E-4</v>
       </c>
       <c r="C34">
         <v>33</v>
       </c>
       <c r="D34" s="1">
-        <v>3.9949651889824203E-4</v>
+        <v>3.6748909317515903E-4</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -10840,13 +10840,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="1">
-        <v>3.5082951848556501E-4</v>
+        <v>3.4787215523345602E-4</v>
       </c>
       <c r="C35">
         <v>34</v>
       </c>
       <c r="D35" s="1">
-        <v>4.01170572958099E-4</v>
+        <v>3.6503228597748702E-4</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -10854,13 +10854,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="1">
-        <v>3.5102780908237901E-4</v>
+        <v>3.4451959389052497E-4</v>
       </c>
       <c r="C36">
         <v>35</v>
       </c>
       <c r="D36" s="1">
-        <v>4.0429476296078399E-4</v>
+        <v>3.5653113592081501E-4</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -10868,13 +10868,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="1">
-        <v>3.4800927330132703E-4</v>
+        <v>3.42780085589735E-4</v>
       </c>
       <c r="C37">
         <v>36</v>
       </c>
       <c r="D37" s="1">
-        <v>4.1313147620511902E-4</v>
+        <v>3.5589290463310401E-4</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -10882,13 +10882,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="1">
-        <v>3.5367302098830602E-4</v>
+        <v>3.4739502557412199E-4</v>
       </c>
       <c r="C38">
         <v>37</v>
       </c>
       <c r="D38" s="1">
-        <v>4.1239352929854802E-4</v>
+        <v>3.56447258703549E-4</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -10896,13 +10896,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="1">
-        <v>3.4944995019321398E-4</v>
+        <v>3.4498752343934698E-4</v>
       </c>
       <c r="C39">
         <v>38</v>
       </c>
       <c r="D39" s="1">
-        <v>4.1656672140509901E-4</v>
+        <v>3.57555889536875E-4</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -10910,13 +10910,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="1">
-        <v>3.5658767991817298E-4</v>
+        <v>3.48219179440788E-4</v>
       </c>
       <c r="C40">
         <v>39</v>
       </c>
       <c r="D40" s="1">
-        <v>3.9622777619184498E-4</v>
+        <v>3.6003311609356098E-4</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -10924,13 +10924,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="1">
-        <v>3.5012071970403502E-4</v>
+        <v>3.4257667715137998E-4</v>
       </c>
       <c r="C41">
         <v>40</v>
       </c>
       <c r="D41" s="1">
-        <v>3.9097798132477598E-4</v>
+        <v>3.5576098203152299E-4</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -10938,13 +10938,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="1">
-        <v>3.3646307805431801E-4</v>
+        <v>3.2941801669786401E-4</v>
       </c>
       <c r="C42">
         <v>41</v>
       </c>
       <c r="D42" s="1">
-        <v>4.0155308482939201E-4</v>
+        <v>3.5252434100742803E-4</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -10952,13 +10952,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="1">
-        <v>3.3880208589706298E-4</v>
+        <v>3.3081987079039801E-4</v>
       </c>
       <c r="C43">
         <v>42</v>
       </c>
       <c r="D43" s="1">
-        <v>3.95903884011385E-4</v>
+        <v>3.48061943014089E-4</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -10966,13 +10966,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="1">
-        <v>3.3657289854348402E-4</v>
+        <v>3.2857429530746001E-4</v>
       </c>
       <c r="C44">
         <v>43</v>
       </c>
       <c r="D44" s="1">
-        <v>3.9830389304178898E-4</v>
+        <v>3.5504635858424902E-4</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -10980,13 +10980,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="1">
-        <v>3.38396341422133E-4</v>
+        <v>3.30348036914934E-4</v>
       </c>
       <c r="C45">
         <v>44</v>
       </c>
       <c r="D45" s="1">
-        <v>3.9288132404300498E-4</v>
+        <v>3.5554445758511201E-4</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -10994,13 +10994,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="1">
-        <v>3.4086490485094999E-4</v>
+        <v>3.3174256342686403E-4</v>
       </c>
       <c r="C46">
         <v>45</v>
       </c>
       <c r="D46" s="1">
-        <v>3.9927963442358099E-4</v>
+        <v>3.5217000114907699E-4</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -11008,13 +11008,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="1">
-        <v>3.31339641448088E-4</v>
+        <v>3.2166727483059999E-4</v>
       </c>
       <c r="C47">
         <v>46</v>
       </c>
       <c r="D47" s="1">
-        <v>3.8739548534710399E-4</v>
+        <v>3.4478517115087501E-4</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -11022,13 +11022,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="1">
-        <v>3.1979769174208698E-4</v>
+        <v>3.1035298959514602E-4</v>
       </c>
       <c r="C48">
         <v>47</v>
       </c>
       <c r="D48" s="1">
-        <v>3.91261413778322E-4</v>
+        <v>3.4450792543391703E-4</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -11036,13 +11036,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="1">
-        <v>3.1633147739676501E-4</v>
+        <v>3.0662098407074402E-4</v>
       </c>
       <c r="C49">
         <v>48</v>
       </c>
       <c r="D49" s="1">
-        <v>3.9451120698353801E-4</v>
+        <v>3.4967363520832197E-4</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -11050,13 +11050,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="1">
-        <v>3.1904142562728997E-4</v>
+        <v>3.1006985954753103E-4</v>
       </c>
       <c r="C50">
         <v>49</v>
       </c>
       <c r="D50" s="1">
-        <v>3.9038156859295199E-4</v>
+        <v>3.41057159787945E-4</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -11064,13 +11064,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="1">
-        <v>3.1524407852689002E-4</v>
+        <v>3.0741872872216302E-4</v>
       </c>
       <c r="C51">
         <v>50</v>
       </c>
       <c r="D51" s="1">
-        <v>3.8622455702593401E-4</v>
+        <v>3.5092827219385499E-4</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -11078,13 +11078,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="1">
-        <v>3.1398976210366601E-4</v>
+        <v>3.0512274614305599E-4</v>
       </c>
       <c r="C52">
         <v>51</v>
       </c>
       <c r="D52" s="1">
-        <v>3.8946630727969901E-4</v>
+        <v>3.4671952436666998E-4</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -11092,13 +11092,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="1">
-        <v>3.1228635063619E-4</v>
+        <v>3.0335668383452401E-4</v>
       </c>
       <c r="C53">
         <v>52</v>
       </c>
       <c r="D53" s="1">
-        <v>3.7631392000020701E-4</v>
+        <v>3.3554561058928597E-4</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -11106,13 +11106,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="1">
-        <v>3.1621012869359499E-4</v>
+        <v>3.0751836824008199E-4</v>
       </c>
       <c r="C54">
         <v>53</v>
       </c>
       <c r="D54" s="1">
-        <v>3.7719577190108898E-4</v>
+        <v>3.2695296051417502E-4</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -11120,13 +11120,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="1">
-        <v>3.0798713378064901E-4</v>
+        <v>2.99613913546561E-4</v>
       </c>
       <c r="C55">
         <v>54</v>
       </c>
       <c r="D55" s="1">
-        <v>3.8028280381384802E-4</v>
+        <v>3.2719746783496098E-4</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -11134,13 +11134,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="1">
-        <v>3.16211758354541E-4</v>
+        <v>3.1014797633432701E-4</v>
       </c>
       <c r="C56">
         <v>55</v>
       </c>
       <c r="D56" s="1">
-        <v>3.8233539870019198E-4</v>
+        <v>3.27473703643635E-4</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -11148,13 +11148,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="1">
-        <v>3.1279779739524702E-4</v>
+        <v>3.07479503562066E-4</v>
       </c>
       <c r="C57">
         <v>56</v>
       </c>
       <c r="D57" s="1">
-        <v>3.8383433552139002E-4</v>
+        <v>3.1815063043047102E-4</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -11162,13 +11162,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="1">
-        <v>3.12885506473467E-4</v>
+        <v>3.0644010509891102E-4</v>
       </c>
       <c r="C58">
         <v>57</v>
       </c>
       <c r="D58" s="1">
-        <v>3.8097738739993901E-4</v>
+        <v>3.2735932898918702E-4</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -11176,13 +11176,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="1">
-        <v>3.1140773317617503E-4</v>
+        <v>3.0417122419283601E-4</v>
       </c>
       <c r="C59">
         <v>58</v>
       </c>
       <c r="D59" s="1">
-        <v>3.8222149940857902E-4</v>
+        <v>3.2650772858947897E-4</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -11190,13 +11190,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="1">
-        <v>3.1206531355423199E-4</v>
+        <v>3.0504684849950298E-4</v>
       </c>
       <c r="C60">
         <v>59</v>
       </c>
       <c r="D60" s="1">
-        <v>3.78760028931395E-4</v>
+        <v>3.2715330616477198E-4</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -11204,13 +11204,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="1">
-        <v>3.1623898762415102E-4</v>
+        <v>3.1087107174923502E-4</v>
       </c>
       <c r="C61">
         <v>60</v>
       </c>
       <c r="D61" s="1">
-        <v>3.7455425911435598E-4</v>
+        <v>3.26119143384753E-4</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -11218,13 +11218,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="1">
-        <v>3.0798550473855102E-4</v>
+        <v>3.0149487324967702E-4</v>
       </c>
       <c r="C62">
         <v>61</v>
       </c>
       <c r="D62" s="1">
-        <v>3.7072332230313697E-4</v>
+        <v>3.2185131927681701E-4</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -11232,13 +11232,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="1">
-        <v>3.08075534056743E-4</v>
+        <v>3.0255436832057702E-4</v>
       </c>
       <c r="C63">
         <v>62</v>
       </c>
       <c r="D63" s="1">
-        <v>3.6316677801223601E-4</v>
+        <v>3.2322491950519903E-4</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -11246,13 +11246,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="1">
-        <v>3.04940745985122E-4</v>
+        <v>2.97438729777713E-4</v>
       </c>
       <c r="C64">
         <v>63</v>
       </c>
       <c r="D64" s="1">
-        <v>3.5427950006193803E-4</v>
+        <v>3.1002704032439502E-4</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -11260,13 +11260,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="1">
-        <v>3.0519287959425098E-4</v>
+        <v>2.9753249213139302E-4</v>
       </c>
       <c r="C65">
         <v>64</v>
       </c>
       <c r="D65" s="1">
-        <v>3.5098998913497299E-4</v>
+        <v>3.1055767779179902E-4</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -11274,13 +11274,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="1">
-        <v>3.12792705353473E-4</v>
+        <v>3.0660315413073901E-4</v>
       </c>
       <c r="C66">
         <v>65</v>
       </c>
       <c r="D66" s="1">
-        <v>3.4879522474423499E-4</v>
+        <v>3.1535592702067801E-4</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -11288,13 +11288,13 @@
         <v>66</v>
       </c>
       <c r="B67" s="1">
-        <v>3.0113278074980299E-4</v>
+        <v>2.9766167949058902E-4</v>
       </c>
       <c r="C67">
         <v>66</v>
       </c>
       <c r="D67" s="1">
-        <v>3.6394457758151701E-4</v>
+        <v>3.20436735596234E-4</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -11302,13 +11302,13 @@
         <v>67</v>
       </c>
       <c r="B68" s="1">
-        <v>3.0180922307701698E-4</v>
+        <v>2.9649910020974001E-4</v>
       </c>
       <c r="C68">
         <v>67</v>
       </c>
       <c r="D68" s="1">
-        <v>3.5337792221981401E-4</v>
+        <v>3.2646913317759397E-4</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -11316,13 +11316,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="1">
-        <v>2.9598180197460902E-4</v>
+        <v>2.9084415349995597E-4</v>
       </c>
       <c r="C69">
         <v>68</v>
       </c>
       <c r="D69" s="1">
-        <v>3.4898961428167502E-4</v>
+        <v>3.15527392673664E-4</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -11330,13 +11330,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="1">
-        <v>2.9677232784032102E-4</v>
+        <v>2.9149113701476098E-4</v>
       </c>
       <c r="C70">
         <v>69</v>
       </c>
       <c r="D70" s="1">
-        <v>3.4365049754743297E-4</v>
+        <v>3.1288051432217499E-4</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -11344,13 +11344,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="1">
-        <v>2.9019498285911302E-4</v>
+        <v>2.88870859121283E-4</v>
       </c>
       <c r="C71">
         <v>70</v>
       </c>
       <c r="D71" s="1">
-        <v>3.45993353399636E-4</v>
+        <v>3.0376232066447702E-4</v>
       </c>
     </row>
   </sheetData>
@@ -11383,13 +11383,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.69443083399468597</v>
+        <v>0.69501886122575696</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0.69636862395738897</v>
+        <v>0.74620112723561005</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -11397,13 +11397,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.70365265435138802</v>
+        <v>0.70422313939555303</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>0.72738753603457995</v>
+        <v>0.76032454361054702</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -11411,13 +11411,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.727148507956623</v>
+        <v>0.727660346524444</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4">
-        <v>0.74627948509629605</v>
+        <v>0.775828157917407</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -11425,13 +11425,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.74026436338123303</v>
+        <v>0.74074246660453502</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>0.75956420768884103</v>
+        <v>0.78945337687731199</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -11439,13 +11439,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.75675915673068905</v>
+        <v>0.75719355402925304</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6">
-        <v>0.77518677336143904</v>
+        <v>0.79771866621765197</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -11453,13 +11453,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.77072946434079603</v>
+        <v>0.77113276997658298</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7">
-        <v>0.78640935597303496</v>
+        <v>0.80505637483325099</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -11467,13 +11467,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.779178861176549</v>
+        <v>0.77956346378253005</v>
       </c>
       <c r="C8">
         <v>7</v>
       </c>
       <c r="D8">
-        <v>0.79660414921792999</v>
+        <v>0.81116780356131202</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -11481,13 +11481,13 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.78969965170493095</v>
+        <v>0.79005701441806897</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
       <c r="D9">
-        <v>0.80312712717736701</v>
+        <v>0.81711944050686403</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -11495,13 +11495,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.79601985836070199</v>
+        <v>0.79636193713272796</v>
       </c>
       <c r="C10">
         <v>9</v>
       </c>
       <c r="D10">
-        <v>0.80861766277383396</v>
+        <v>0.82068109256750199</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -11509,13 +11509,13 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.80071995968100296</v>
+        <v>0.80105293934908495</v>
       </c>
       <c r="C11">
         <v>10</v>
       </c>
       <c r="D11">
-        <v>0.81200768424035297</v>
+        <v>0.82286873370037605</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -11523,13 +11523,13 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.80665864678321098</v>
+        <v>0.80697447664993305</v>
       </c>
       <c r="C12">
         <v>11</v>
       </c>
       <c r="D12">
-        <v>0.81594275978096398</v>
+        <v>0.82525937122285997</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -11537,13 +11537,13 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.81078282218339504</v>
+        <v>0.81108802514482004</v>
       </c>
       <c r="C13">
         <v>12</v>
       </c>
       <c r="D13">
-        <v>0.818907162791086</v>
+        <v>0.82718828071769201</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -11551,13 +11551,13 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.81425283336104204</v>
+        <v>0.814549954184842</v>
       </c>
       <c r="C14">
         <v>13</v>
       </c>
       <c r="D14">
-        <v>0.82152470845580094</v>
+        <v>0.82827565322494301</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -11565,13 +11565,13 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.81714927125713499</v>
+        <v>0.81743933733791696</v>
       </c>
       <c r="C15">
         <v>14</v>
       </c>
       <c r="D15">
-        <v>0.82354635691304501</v>
+        <v>0.82939944290857004</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -11579,13 +11579,13 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.81943763050608898</v>
+        <v>0.81971923531761204</v>
       </c>
       <c r="C16">
         <v>15</v>
       </c>
       <c r="D16">
-        <v>0.82556434571030302</v>
+        <v>0.83029329532372098</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -11593,13 +11593,13 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.82168382524391603</v>
+        <v>0.82195772996990002</v>
       </c>
       <c r="C17">
         <v>16</v>
       </c>
       <c r="D17">
-        <v>0.82703769868032595</v>
+        <v>0.83092055834449297</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -11607,13 +11607,13 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.82357589559722</v>
+        <v>0.823843278224617</v>
       </c>
       <c r="C18">
         <v>17</v>
       </c>
       <c r="D18">
-        <v>0.82804682378109695</v>
+        <v>0.83140554637511999</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -11621,13 +11621,13 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.82555883007989495</v>
+        <v>0.82581609717512305</v>
       </c>
       <c r="C19">
         <v>18</v>
       </c>
       <c r="D19">
-        <v>0.82896921494019604</v>
+        <v>0.83190437032221998</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -11635,13 +11635,13 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.82698045114197005</v>
+        <v>0.82722942299007196</v>
       </c>
       <c r="C20">
         <v>19</v>
       </c>
       <c r="D20">
-        <v>0.82988020887248004</v>
+        <v>0.83222217871305004</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -11649,13 +11649,13 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.82837648072457004</v>
+        <v>0.82862076797168005</v>
       </c>
       <c r="C21">
         <v>20</v>
       </c>
       <c r="D21">
-        <v>0.83058461499854097</v>
+        <v>0.83250868660604904</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -11663,13 +11663,13 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0.82927934498359901</v>
+        <v>0.82952096402400599</v>
       </c>
       <c r="C22">
         <v>21</v>
       </c>
       <c r="D22">
-        <v>0.83126379561112596</v>
+        <v>0.83273888492955395</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -11677,13 +11677,13 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.83025231787179199</v>
+        <v>0.83049028744769104</v>
       </c>
       <c r="C23">
         <v>22</v>
       </c>
       <c r="D23">
-        <v>0.83183608801168596</v>
+        <v>0.83311715366482098</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -11691,13 +11691,13 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>0.83081734323323597</v>
+        <v>0.83105453178475397</v>
       </c>
       <c r="C24">
         <v>23</v>
       </c>
       <c r="D24">
-        <v>0.83214598279123297</v>
+        <v>0.83333341164984098</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -11705,13 +11705,13 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0.83140633936759001</v>
+        <v>0.83163926894149998</v>
       </c>
       <c r="C25">
         <v>24</v>
       </c>
       <c r="D25">
-        <v>0.83264688568163203</v>
+        <v>0.83371992972398601</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -11719,13 +11719,13 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>0.83190036732530004</v>
+        <v>0.83213234967798799</v>
       </c>
       <c r="C26">
         <v>25</v>
       </c>
       <c r="D26">
-        <v>0.83313769836664098</v>
+        <v>0.83405632523279505</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -11733,13 +11733,13 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>0.83246526198460202</v>
+        <v>0.83269471441885201</v>
       </c>
       <c r="C27">
         <v>26</v>
       </c>
       <c r="D27">
-        <v>0.83339152192711397</v>
+        <v>0.83422543667979698</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -11747,13 +11747,13 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>0.83285174821957497</v>
+        <v>0.83307919626378002</v>
       </c>
       <c r="C28">
         <v>27</v>
       </c>
       <c r="D28">
-        <v>0.83358781040451801</v>
+        <v>0.834378571559098</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -11761,13 +11761,13 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>0.83322563476802403</v>
+        <v>0.83345208726547404</v>
       </c>
       <c r="C29">
         <v>28</v>
       </c>
       <c r="D29">
-        <v>0.83374862632048397</v>
+        <v>0.83444968294866795</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -11775,13 +11775,13 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>0.83352164898005199</v>
+        <v>0.833747366607407</v>
       </c>
       <c r="C30">
         <v>29</v>
       </c>
       <c r="D30">
-        <v>0.83380208349671103</v>
+        <v>0.834578826870916</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -11789,13 +11789,13 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.83376980006754597</v>
+        <v>0.83399484677375102</v>
       </c>
       <c r="C31">
         <v>30</v>
       </c>
       <c r="D31">
-        <v>0.83400352163852298</v>
+        <v>0.83457261376125402</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -11803,13 +11803,13 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>0.83403661542096996</v>
+        <v>0.83426007868198504</v>
       </c>
       <c r="C32">
         <v>31</v>
       </c>
       <c r="D32">
-        <v>0.83415194699139295</v>
+        <v>0.83465910129196097</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -11817,13 +11817,13 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.834272794192224</v>
+        <v>0.83449570695006703</v>
       </c>
       <c r="C33">
         <v>32</v>
       </c>
       <c r="D33">
-        <v>0.83432944050072499</v>
+        <v>0.83477302570608802</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -11831,13 +11831,13 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>0.834525833539842</v>
+        <v>0.83474830379495601</v>
       </c>
       <c r="C34">
         <v>33</v>
       </c>
       <c r="D34">
-        <v>0.83447946041973098</v>
+        <v>0.83501082073090105</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -11845,13 +11845,13 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>0.83470275195974697</v>
+        <v>0.83492509025977601</v>
       </c>
       <c r="C35">
         <v>34</v>
       </c>
       <c r="D35">
-        <v>0.83455667924544097</v>
+        <v>0.83502724109214899</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -11859,13 +11859,13 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>0.83474235470888403</v>
+        <v>0.83496479672950197</v>
       </c>
       <c r="C36">
         <v>35</v>
       </c>
       <c r="D36">
-        <v>0.83459607287114901</v>
+        <v>0.83514017349717096</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -11873,13 +11873,13 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0.83497675593100096</v>
+        <v>0.83519831045185999</v>
       </c>
       <c r="C37">
         <v>36</v>
       </c>
       <c r="D37">
-        <v>0.83480532700107601</v>
+        <v>0.83526621086458797</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -11887,13 +11887,13 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>0.83503578101849296</v>
+        <v>0.83525694341110102</v>
       </c>
       <c r="C38">
         <v>37</v>
       </c>
       <c r="D38">
-        <v>0.83499115930709</v>
+        <v>0.83534567601504695</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -11901,13 +11901,13 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>0.83517978863895104</v>
+        <v>0.83540068030940196</v>
       </c>
       <c r="C39">
         <v>38</v>
       </c>
       <c r="D39">
-        <v>0.83512669742872303</v>
+        <v>0.835218751060536</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -11915,13 +11915,13 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>0.83520203414358096</v>
+        <v>0.83542206071617797</v>
       </c>
       <c r="C40">
         <v>39</v>
       </c>
       <c r="D40">
-        <v>0.83518854568249001</v>
+        <v>0.83531795197109604</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -11929,13 +11929,13 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>0.83525345236638804</v>
+        <v>0.83547351466215503</v>
       </c>
       <c r="C41">
         <v>40</v>
       </c>
       <c r="D41">
-        <v>0.83526234011206901</v>
+        <v>0.83548139852399395</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -11943,13 +11943,13 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>0.83532939031110198</v>
+        <v>0.83554906398719697</v>
       </c>
       <c r="C42">
         <v>41</v>
       </c>
       <c r="D42">
-        <v>0.83530897463646503</v>
+        <v>0.83550562443057297</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -11957,13 +11957,13 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>0.83530905305775005</v>
+        <v>0.83552823179598001</v>
       </c>
       <c r="C43">
         <v>42</v>
       </c>
       <c r="D43">
-        <v>0.83530573322333401</v>
+        <v>0.83568549134472003</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -11971,13 +11971,13 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>0.83539970806369401</v>
+        <v>0.83561842630808103</v>
       </c>
       <c r="C44">
         <v>43</v>
       </c>
       <c r="D44">
-        <v>0.83533093259638203</v>
+        <v>0.83569744766499299</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -11985,13 +11985,13 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>0.83544733592437204</v>
+        <v>0.83566580779562505</v>
       </c>
       <c r="C45">
         <v>44</v>
       </c>
       <c r="D45">
-        <v>0.83533561173307902</v>
+        <v>0.83567752916637295</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -11999,13 +11999,13 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>0.83539808735712895</v>
+        <v>0.83561717324394702</v>
       </c>
       <c r="C46">
         <v>45</v>
       </c>
       <c r="D46">
-        <v>0.83543429185056395</v>
+        <v>0.83567938265706998</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -12013,13 +12013,13 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>0.83545481208691597</v>
+        <v>0.835673326180425</v>
       </c>
       <c r="C47">
         <v>46</v>
       </c>
       <c r="D47">
-        <v>0.83559889812865895</v>
+        <v>0.835752608592365</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -12027,13 +12027,13 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>0.83548625902236895</v>
+        <v>0.83570480941677605</v>
       </c>
       <c r="C48">
         <v>47</v>
       </c>
       <c r="D48">
-        <v>0.83556721592934902</v>
+        <v>0.83575816906445699</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -12041,13 +12041,13 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>0.83551341892755204</v>
+        <v>0.83573159366262795</v>
       </c>
       <c r="C49">
         <v>48</v>
       </c>
       <c r="D49">
-        <v>0.83549972134303196</v>
+        <v>0.83575756863789297</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -12055,13 +12055,13 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>0.83555323080011601</v>
+        <v>0.83577124792134905</v>
       </c>
       <c r="C50">
         <v>49</v>
       </c>
       <c r="D50">
-        <v>0.83560190427793302</v>
+        <v>0.83574368051041403</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -12069,13 +12069,13 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>0.83545076032050203</v>
+        <v>0.83566875771743898</v>
       </c>
       <c r="C51">
         <v>50</v>
       </c>
       <c r="D51">
-        <v>0.83558940915312296</v>
+        <v>0.83579205400706402</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -12083,13 +12083,13 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>0.83550108064531303</v>
+        <v>0.83571901081028799</v>
       </c>
       <c r="C52">
         <v>51</v>
       </c>
       <c r="D52">
-        <v>0.83553488021932798</v>
+        <v>0.83576641840333499</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -12097,13 +12097,13 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>0.83563133840039405</v>
+        <v>0.83584896400312203</v>
       </c>
       <c r="C53">
         <v>52</v>
       </c>
       <c r="D53">
-        <v>0.83561881713515496</v>
+        <v>0.83585588196135796</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -12111,13 +12111,13 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>0.83570419177454802</v>
+        <v>0.83592224214942201</v>
       </c>
       <c r="C54">
         <v>53</v>
       </c>
       <c r="D54">
-        <v>0.83566296831884601</v>
+        <v>0.83597455757699102</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -12125,13 +12125,13 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>0.83582833266936596</v>
+        <v>0.83604613886561097</v>
       </c>
       <c r="C55">
         <v>54</v>
       </c>
       <c r="D55">
-        <v>0.83563680174994404</v>
+        <v>0.83601100085887103</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -12139,13 +12139,13 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>0.83576739933059496</v>
+        <v>0.83598591347069995</v>
       </c>
       <c r="C56">
         <v>55</v>
       </c>
       <c r="D56">
-        <v>0.83548484743923102</v>
+        <v>0.83597513189805195</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -12153,13 +12153,13 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>0.83575882527005596</v>
+        <v>0.83597659380620803</v>
       </c>
       <c r="C57">
         <v>56</v>
       </c>
       <c r="D57">
-        <v>0.83552016315809796</v>
+        <v>0.83590843233845202</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -12167,13 +12167,13 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>0.8356752281798</v>
+        <v>0.83589287345879604</v>
       </c>
       <c r="C58">
         <v>57</v>
       </c>
       <c r="D58">
-        <v>0.835582769484291</v>
+        <v>0.835877236262631</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -12181,13 +12181,13 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>0.83571344548622695</v>
+        <v>0.83593101359835598</v>
       </c>
       <c r="C59">
         <v>58</v>
       </c>
       <c r="D59">
-        <v>0.83560475358463704</v>
+        <v>0.83594761669812401</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -12195,13 +12195,13 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>0.83583382215934499</v>
+        <v>0.83605107280563595</v>
       </c>
       <c r="C60">
         <v>59</v>
       </c>
       <c r="D60">
-        <v>0.83564150702706996</v>
+        <v>0.83589480526600202</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -12209,13 +12209,13 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>0.83578980167779704</v>
+        <v>0.836006928400437</v>
       </c>
       <c r="C61">
         <v>60</v>
       </c>
       <c r="D61">
-        <v>0.83568199855077396</v>
+        <v>0.83590208870127702</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -12223,13 +12223,13 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>0.83579207589507398</v>
+        <v>0.83600909515716804</v>
       </c>
       <c r="C62">
         <v>61</v>
       </c>
       <c r="D62">
-        <v>0.83569363104144401</v>
+        <v>0.83596463748593497</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -12237,13 +12237,13 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>0.83586126960924201</v>
+        <v>0.836078274739532</v>
       </c>
       <c r="C63">
         <v>62</v>
       </c>
       <c r="D63">
-        <v>0.83571561514179005</v>
+        <v>0.83596526401800197</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -12251,13 +12251,13 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>0.83583800462790103</v>
+        <v>0.83605511915856701</v>
       </c>
       <c r="C64">
         <v>63</v>
       </c>
       <c r="D64">
-        <v>0.83583578269148096</v>
+        <v>0.83600823367557597</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -12265,13 +12265,13 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>0.83585138852727903</v>
+        <v>0.83606848517598997</v>
       </c>
       <c r="C65">
         <v>64</v>
       </c>
       <c r="D65">
-        <v>0.83588976267627701</v>
+        <v>0.83599625124980004</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -12279,13 +12279,13 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>0.83575856386577196</v>
+        <v>0.83597607169615296</v>
       </c>
       <c r="C66">
         <v>65</v>
       </c>
       <c r="D66">
-        <v>0.835877555096181</v>
+        <v>0.83593881914368695</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -12293,13 +12293,13 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>0.83590377394593895</v>
+        <v>0.83612053954853105</v>
       </c>
       <c r="C67">
         <v>66</v>
       </c>
       <c r="D67">
-        <v>0.83573213589258499</v>
+        <v>0.83587671415257603</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -12307,13 +12307,13 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>0.83589099127641597</v>
+        <v>0.83610842659524198</v>
       </c>
       <c r="C68">
         <v>67</v>
       </c>
       <c r="D68">
-        <v>0.835710047230526</v>
+        <v>0.83593208392397</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -12321,13 +12321,13 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>0.83594708863591904</v>
+        <v>0.836163900788647</v>
       </c>
       <c r="C69">
         <v>68</v>
       </c>
       <c r="D69">
-        <v>0.83575080015851499</v>
+        <v>0.83604475527396405</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -12335,13 +12335,13 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>0.83595822445844803</v>
+        <v>0.83617525668235604</v>
       </c>
       <c r="C70">
         <v>69</v>
       </c>
       <c r="D70">
-        <v>0.83579411484849497</v>
+        <v>0.83601684849149305</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -12349,13 +12349,13 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>0.83597796048194495</v>
+        <v>0.83619478359843402</v>
       </c>
       <c r="C71">
         <v>70</v>
       </c>
       <c r="D71">
-        <v>0.83585214659970497</v>
+        <v>0.83612398547489797</v>
       </c>
     </row>
   </sheetData>
@@ -12388,13 +12388,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.26692267867640501</v>
+        <v>0.24248137726896299</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0.234109042658696</v>
+        <v>0.112178219518469</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -12402,13 +12402,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.25403799899908702</v>
+        <v>0.23004055393266701</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>0.16807668836870199</v>
+        <v>9.1656116116686795E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -12416,13 +12416,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.21216988915584101</v>
+        <v>0.189787226376332</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4">
-        <v>0.156084854534493</v>
+        <v>6.8421978091273802E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -12430,13 +12430,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.19266997775228401</v>
+        <v>0.17223807650233</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>0.14485280444220899</v>
+        <v>5.6196211089671697E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -12444,13 +12444,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.154116802701043</v>
+        <v>0.136011819474154</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6">
-        <v>0.135395127061051</v>
+        <v>5.0797121470985702E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -12458,13 +12458,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.14289300300110599</v>
+        <v>0.12531785011733801</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7">
-        <v>0.10271012935615501</v>
+        <v>4.3063735614371899E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -12472,13 +12472,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.12481310405547801</v>
+        <v>0.108573448887503</v>
       </c>
       <c r="C8">
         <v>7</v>
       </c>
       <c r="D8">
-        <v>8.76860482259577E-2</v>
+        <v>3.9981009317382299E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -12486,13 +12486,13 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.10708154494326701</v>
+        <v>9.2017140764154098E-2</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
       <c r="D9">
-        <v>6.8142895613655302E-2</v>
+        <v>3.2538260770773299E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -12500,13 +12500,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>9.9285162137684402E-2</v>
+        <v>8.5021307464880999E-2</v>
       </c>
       <c r="C10">
         <v>9</v>
       </c>
       <c r="D10">
-        <v>5.9257300058918903E-2</v>
+        <v>3.0035721551089599E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -12514,13 +12514,13 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>9.3486067991894503E-2</v>
+        <v>7.9633172787232698E-2</v>
       </c>
       <c r="C11">
         <v>10</v>
       </c>
       <c r="D11">
-        <v>5.95883531661986E-2</v>
+        <v>2.8965586295757701E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -12528,13 +12528,13 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>8.3695020397505496E-2</v>
+        <v>7.0574262899208595E-2</v>
       </c>
       <c r="C12">
         <v>11</v>
       </c>
       <c r="D12">
-        <v>4.8807878090847301E-2</v>
+        <v>2.3234866493898401E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -12542,13 +12542,13 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>7.6165621867725394E-2</v>
+        <v>6.3803051088916596E-2</v>
       </c>
       <c r="C13">
         <v>12</v>
       </c>
       <c r="D13">
-        <v>4.3516922080397702E-2</v>
+        <v>1.9756211494142899E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -12556,13 +12556,13 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>7.3337319331953199E-2</v>
+        <v>6.1118216980817E-2</v>
       </c>
       <c r="C14">
         <v>13</v>
       </c>
       <c r="D14">
-        <v>3.6410822924478399E-2</v>
+        <v>1.8278307958744099E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -12570,13 +12570,13 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>6.8877785950775094E-2</v>
+        <v>5.7130168985491503E-2</v>
       </c>
       <c r="C15">
         <v>14</v>
       </c>
       <c r="D15">
-        <v>3.5964746092669302E-2</v>
+        <v>1.4980437357110099E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -12584,13 +12584,13 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>6.2276506883994699E-2</v>
+        <v>5.1926189615518002E-2</v>
       </c>
       <c r="C16">
         <v>15</v>
       </c>
       <c r="D16">
-        <v>3.16092764502134E-2</v>
+        <v>1.3816162884028401E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -12598,13 +12598,13 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>5.1661968765753602E-2</v>
+        <v>4.2730043039346202E-2</v>
       </c>
       <c r="C17">
         <v>16</v>
       </c>
       <c r="D17">
-        <v>2.6169221569723299E-2</v>
+        <v>1.3032464636151901E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -12612,13 +12612,13 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>4.8821097587909597E-2</v>
+        <v>4.0386255013246303E-2</v>
       </c>
       <c r="C18">
         <v>17</v>
       </c>
       <c r="D18">
-        <v>2.54623950742787E-2</v>
+        <v>1.24627273504288E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -12626,13 +12626,13 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>3.80017828620254E-2</v>
+        <v>3.1356207532817301E-2</v>
       </c>
       <c r="C19">
         <v>18</v>
       </c>
       <c r="D19">
-        <v>2.4827873436180301E-2</v>
+        <v>1.11809475974738E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -12640,13 +12640,13 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>3.1337886635957601E-2</v>
+        <v>2.6342982259605199E-2</v>
       </c>
       <c r="C20">
         <v>19</v>
       </c>
       <c r="D20">
-        <v>2.21413654640846E-2</v>
+        <v>1.10261351850261E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -12654,13 +12654,13 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>2.5235854112321699E-2</v>
+        <v>2.11680008709015E-2</v>
       </c>
       <c r="C21">
         <v>20</v>
       </c>
       <c r="D21">
-        <v>2.1014724820395798E-2</v>
+        <v>1.0635982241785301E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -12668,13 +12668,13 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>2.38501221870107E-2</v>
+        <v>2.0201696385246899E-2</v>
       </c>
       <c r="C22">
         <v>21</v>
       </c>
       <c r="D22">
-        <v>1.7896974561768399E-2</v>
+        <v>1.04758374638396E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -12682,13 +12682,13 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>2.0788834142309798E-2</v>
+        <v>1.8066853195488598E-2</v>
       </c>
       <c r="C23">
         <v>22</v>
       </c>
       <c r="D23">
-        <v>1.7149501319780401E-2</v>
+        <v>1.03730969487186E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -12696,13 +12696,13 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>1.9958825861053998E-2</v>
+        <v>1.72020102657434E-2</v>
       </c>
       <c r="C24">
         <v>23</v>
       </c>
       <c r="D24">
-        <v>1.5332619965648501E-2</v>
+        <v>1.0066406157444301E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -12710,13 +12710,13 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>1.7209555556019201E-2</v>
+        <v>1.5445119038144099E-2</v>
       </c>
       <c r="C25">
         <v>24</v>
       </c>
       <c r="D25">
-        <v>1.45897031831996E-2</v>
+        <v>9.5061967776241506E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -12724,13 +12724,13 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>1.64519311431209E-2</v>
+        <v>1.4671403373588E-2</v>
       </c>
       <c r="C26">
         <v>25</v>
       </c>
       <c r="D26">
-        <v>1.24479952869033E-2</v>
+        <v>8.7324075435115008E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -12738,13 +12738,13 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>1.42770552158487E-2</v>
+        <v>1.28258802773508E-2</v>
       </c>
       <c r="C27">
         <v>26</v>
       </c>
       <c r="D27">
-        <v>1.13246803789808E-2</v>
+        <v>8.4479202395479902E-3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -12752,13 +12752,13 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>1.26642233332037E-2</v>
+        <v>1.1641768169204101E-2</v>
       </c>
       <c r="C28">
         <v>27</v>
       </c>
       <c r="D28">
-        <v>1.0729618711685001E-2</v>
+        <v>8.3473585235140802E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -12766,13 +12766,13 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>1.21851419208609E-2</v>
+        <v>1.13048966529794E-2</v>
       </c>
       <c r="C29">
         <v>28</v>
       </c>
       <c r="D29">
-        <v>1.0251855562514799E-2</v>
+        <v>8.2800714985148995E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -12780,13 +12780,13 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>1.19402811650997E-2</v>
+        <v>1.11441615016592E-2</v>
       </c>
       <c r="C30">
         <v>29</v>
       </c>
       <c r="D30">
-        <v>1.0258081598604101E-2</v>
+        <v>8.0331553662165208E-3</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -12794,13 +12794,13 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>1.1500311220712E-2</v>
+        <v>1.0939779823652299E-2</v>
       </c>
       <c r="C31">
         <v>30</v>
       </c>
       <c r="D31">
-        <v>9.6158464703729792E-3</v>
+        <v>8.0180870732983207E-3</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -12808,13 +12808,13 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>1.03342810766698E-2</v>
+        <v>9.9838943432741592E-3</v>
       </c>
       <c r="C32">
         <v>31</v>
       </c>
       <c r="D32">
-        <v>9.5523033520374598E-3</v>
+        <v>8.1060164032116903E-3</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -12822,13 +12822,13 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>1.02580609014465E-2</v>
+        <v>9.9584331293547899E-3</v>
       </c>
       <c r="C33">
         <v>32</v>
       </c>
       <c r="D33">
-        <v>8.7211348089341299E-3</v>
+        <v>7.98294476008439E-3</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -12836,13 +12836,13 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>1.0097684991696901E-2</v>
+        <v>9.8335404521747195E-3</v>
       </c>
       <c r="C34">
         <v>33</v>
       </c>
       <c r="D34">
-        <v>8.6563172782411404E-3</v>
+        <v>7.6825102723703E-3</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -12850,13 +12850,13 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>1.0011447068847899E-2</v>
+        <v>9.7849030792353693E-3</v>
       </c>
       <c r="C35">
         <v>34</v>
       </c>
       <c r="D35">
-        <v>8.0988837236738494E-3</v>
+        <v>7.7027839226647904E-3</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -12864,13 +12864,13 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>9.9403142157282499E-3</v>
+        <v>9.6588041175554792E-3</v>
       </c>
       <c r="C36">
         <v>35</v>
       </c>
       <c r="D36">
-        <v>8.2032448724222596E-3</v>
+        <v>7.5885399988517297E-3</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -12878,13 +12878,13 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>9.2390872854716099E-3</v>
+        <v>9.1182067013671209E-3</v>
       </c>
       <c r="C37">
         <v>36</v>
       </c>
       <c r="D37">
-        <v>7.8069959868625298E-3</v>
+        <v>7.4967387326986103E-3</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -12892,13 +12892,13 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>9.1335043510130196E-3</v>
+        <v>9.1252426987026708E-3</v>
       </c>
       <c r="C38">
         <v>37</v>
       </c>
       <c r="D38">
-        <v>7.54934772437165E-3</v>
+        <v>7.3873908810105204E-3</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -12906,13 +12906,13 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>9.0093052187663909E-3</v>
+        <v>9.0231117517948004E-3</v>
       </c>
       <c r="C39">
         <v>38</v>
       </c>
       <c r="D39">
-        <v>7.4988519453889997E-3</v>
+        <v>7.7056685704100904E-3</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -12920,13 +12920,13 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>8.5206890569446605E-3</v>
+        <v>8.8316953841792601E-3</v>
       </c>
       <c r="C40">
         <v>39</v>
       </c>
       <c r="D40">
-        <v>7.5657005777816904E-3</v>
+        <v>7.6223554587906998E-3</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -12934,13 +12934,13 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>8.3028261676686092E-3</v>
+        <v>8.5955502032807503E-3</v>
       </c>
       <c r="C41">
         <v>40</v>
       </c>
       <c r="D41">
-        <v>7.5058346124321097E-3</v>
+        <v>7.4501702088706203E-3</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -12948,13 +12948,13 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>8.1898249803878699E-3</v>
+        <v>8.5485810336897502E-3</v>
       </c>
       <c r="C42">
         <v>41</v>
       </c>
       <c r="D42">
-        <v>7.5228260207036097E-3</v>
+        <v>7.1867459255916099E-3</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -12962,13 +12962,13 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>8.0587852198404902E-3</v>
+        <v>8.4828749146463097E-3</v>
       </c>
       <c r="C43">
         <v>42</v>
       </c>
       <c r="D43">
-        <v>7.5351286662872601E-3</v>
+        <v>7.0336575306717301E-3</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -12976,13 +12976,13 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>7.8837247689700907E-3</v>
+        <v>8.3997347071112591E-3</v>
       </c>
       <c r="C44">
         <v>43</v>
       </c>
       <c r="D44">
-        <v>7.4440450941545997E-3</v>
+        <v>7.0479932250102403E-3</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -12990,13 +12990,13 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>7.8297850466704996E-3</v>
+        <v>8.3957578879880704E-3</v>
       </c>
       <c r="C45">
         <v>44</v>
       </c>
       <c r="D45">
-        <v>7.2054063399408803E-3</v>
+        <v>7.2644465288397098E-3</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -13004,13 +13004,13 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>7.6367853810237196E-3</v>
+        <v>7.9961705187613901E-3</v>
       </c>
       <c r="C46">
         <v>45</v>
       </c>
       <c r="D46">
-        <v>7.0885347152659E-3</v>
+        <v>7.16653461983798E-3</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -13018,13 +13018,13 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>7.4777400547704201E-3</v>
+        <v>7.9205045917461192E-3</v>
       </c>
       <c r="C47">
         <v>46</v>
       </c>
       <c r="D47">
-        <v>6.8325836493460801E-3</v>
+        <v>7.0961338047883498E-3</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -13032,13 +13032,13 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>7.4554524753531904E-3</v>
+        <v>7.8648687798054794E-3</v>
       </c>
       <c r="C48">
         <v>47</v>
       </c>
       <c r="D48">
-        <v>6.9013491485816402E-3</v>
+        <v>7.0768978913993402E-3</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -13046,13 +13046,13 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>7.4291705578077199E-3</v>
+        <v>7.8912935688166298E-3</v>
       </c>
       <c r="C49">
         <v>48</v>
       </c>
       <c r="D49">
-        <v>7.0304840689678601E-3</v>
+        <v>7.0998361946441801E-3</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -13060,13 +13060,13 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>7.48158767878638E-3</v>
+        <v>7.9154328743084104E-3</v>
       </c>
       <c r="C50">
         <v>49</v>
       </c>
       <c r="D50">
-        <v>6.8167828213080697E-3</v>
+        <v>7.1727181135409403E-3</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -13074,13 +13074,13 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>7.6424287520163899E-3</v>
+        <v>8.0848900389158505E-3</v>
       </c>
       <c r="C51">
         <v>50</v>
       </c>
       <c r="D51">
-        <v>6.8941721498653403E-3</v>
+        <v>7.0731563384426798E-3</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -13088,13 +13088,13 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>7.6847223624788696E-3</v>
+        <v>8.1020526939969799E-3</v>
       </c>
       <c r="C52">
         <v>51</v>
       </c>
       <c r="D52">
-        <v>6.8152108553856004E-3</v>
+        <v>7.2057541422606598E-3</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -13102,13 +13102,13 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>7.5203255638044099E-3</v>
+        <v>7.9998175810887702E-3</v>
       </c>
       <c r="C53">
         <v>52</v>
       </c>
       <c r="D53">
-        <v>6.7567921983850898E-3</v>
+        <v>7.0195338789596998E-3</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -13116,13 +13116,13 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>7.28861227066014E-3</v>
+        <v>7.72735885005794E-3</v>
       </c>
       <c r="C54">
         <v>53</v>
       </c>
       <c r="D54">
-        <v>6.6934885390288199E-3</v>
+        <v>6.9044677173707202E-3</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -13130,13 +13130,13 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>7.24450810327889E-3</v>
+        <v>7.6890506909253198E-3</v>
       </c>
       <c r="C55">
         <v>54</v>
       </c>
       <c r="D55">
-        <v>6.7002705054229504E-3</v>
+        <v>6.9053820821742403E-3</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -13144,13 +13144,13 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>7.3643567891827104E-3</v>
+        <v>7.8508997318125495E-3</v>
       </c>
       <c r="C56">
         <v>55</v>
       </c>
       <c r="D56">
-        <v>6.9144437437235499E-3</v>
+        <v>6.98845962606311E-3</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -13158,13 +13158,13 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>7.4251359718250903E-3</v>
+        <v>7.9772810610362396E-3</v>
       </c>
       <c r="C57">
         <v>56</v>
       </c>
       <c r="D57">
-        <v>6.8885802080286803E-3</v>
+        <v>7.1478716323320601E-3</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -13172,13 +13172,13 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>7.5204550743036298E-3</v>
+        <v>8.0813481735217893E-3</v>
       </c>
       <c r="C58">
         <v>57</v>
       </c>
       <c r="D58">
-        <v>6.6920275220475802E-3</v>
+        <v>7.08605930925023E-3</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -13186,13 +13186,13 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>7.5439761160470001E-3</v>
+        <v>8.0724134760579193E-3</v>
       </c>
       <c r="C59">
         <v>58</v>
       </c>
       <c r="D59">
-        <v>6.6997672563816699E-3</v>
+        <v>7.0580925189797396E-3</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -13200,13 +13200,13 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>7.3308709942068503E-3</v>
+        <v>7.9055746589497596E-3</v>
       </c>
       <c r="C60">
         <v>59</v>
       </c>
       <c r="D60">
-        <v>6.67972880720421E-3</v>
+        <v>7.06873024478672E-3</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -13214,13 +13214,13 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>7.34612270156849E-3</v>
+        <v>7.9165328697383998E-3</v>
       </c>
       <c r="C61">
         <v>60</v>
       </c>
       <c r="D61">
-        <v>6.70085043252403E-3</v>
+        <v>7.1408693089871503E-3</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -13228,13 +13228,13 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>7.4544914343737598E-3</v>
+        <v>8.0204828834836601E-3</v>
       </c>
       <c r="C62">
         <v>61</v>
       </c>
       <c r="D62">
-        <v>6.8043968461183602E-3</v>
+        <v>7.1574243929256598E-3</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -13242,13 +13242,13 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>7.1630371376724001E-3</v>
+        <v>7.6265958013140402E-3</v>
       </c>
       <c r="C63">
         <v>62</v>
       </c>
       <c r="D63">
-        <v>6.7120767264596797E-3</v>
+        <v>7.1588509762967999E-3</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -13256,13 +13256,13 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>7.3632637374624298E-3</v>
+        <v>7.8505179595205893E-3</v>
       </c>
       <c r="C64">
         <v>63</v>
       </c>
       <c r="D64">
-        <v>6.5800666315721E-3</v>
+        <v>7.03841821743345E-3</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -13270,13 +13270,13 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>7.4009930800018201E-3</v>
+        <v>7.9668849691686607E-3</v>
       </c>
       <c r="C65">
         <v>64</v>
       </c>
       <c r="D65">
-        <v>6.6161681612734802E-3</v>
+        <v>7.1353013202611502E-3</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -13284,13 +13284,13 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>7.4473096305478397E-3</v>
+        <v>7.9923870511095594E-3</v>
       </c>
       <c r="C66">
         <v>65</v>
       </c>
       <c r="D66">
-        <v>6.5501295176829703E-3</v>
+        <v>7.3076983688676904E-3</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -13298,13 +13298,13 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>7.3042233038313302E-3</v>
+        <v>7.8430296499875894E-3</v>
       </c>
       <c r="C67">
         <v>66</v>
       </c>
       <c r="D67">
-        <v>6.7681040598583297E-3</v>
+        <v>7.4165157683646898E-3</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -13312,13 +13312,13 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>7.2511637291851703E-3</v>
+        <v>7.8378116175624908E-3</v>
       </c>
       <c r="C68">
         <v>67</v>
       </c>
       <c r="D68">
-        <v>6.8312880413683996E-3</v>
+        <v>7.4319779104611598E-3</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -13326,13 +13326,13 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>7.1772302582357502E-3</v>
+        <v>7.71473891857518E-3</v>
       </c>
       <c r="C69">
         <v>68</v>
       </c>
       <c r="D69">
-        <v>6.7715277611400098E-3</v>
+        <v>7.24751559154105E-3</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -13340,13 +13340,13 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>7.2046816608610301E-3</v>
+        <v>7.7734293340226898E-3</v>
       </c>
       <c r="C70">
         <v>69</v>
       </c>
       <c r="D70">
-        <v>6.7235627618723003E-3</v>
+        <v>7.2610096244785797E-3</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -13354,13 +13354,13 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>7.3461647539781599E-3</v>
+        <v>7.9331898255848906E-3</v>
       </c>
       <c r="C71">
         <v>70</v>
       </c>
       <c r="D71">
-        <v>6.6769066942950197E-3</v>
+        <v>7.0695668347329904E-3</v>
       </c>
     </row>
   </sheetData>
@@ -13393,13 +13393,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.77155569002671098</v>
+        <v>0.77178122555217299</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0.69411711188485103</v>
+        <v>0.65396779990576803</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -13407,13 +13407,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.79372142051421202</v>
+        <v>0.79393219793924297</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>0.75857739221243103</v>
+        <v>0.76069737293129402</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -13421,13 +13421,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.79984229178230204</v>
+        <v>0.80006596616597603</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4">
-        <v>0.77127695107928296</v>
+        <v>0.80975809452680403</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -13435,13 +13435,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.83413450849187998</v>
+        <v>0.83428731992295901</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>0.80406520669412396</v>
+        <v>0.79576459941422295</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -13449,13 +13449,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.83212896486716104</v>
+        <v>0.83223977300482699</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6">
-        <v>0.79646248774501405</v>
+        <v>0.79627198066660998</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -13463,13 +13463,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.828178909382151</v>
+        <v>0.82830132842175697</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7">
-        <v>0.79904692418152701</v>
+        <v>0.810361624910233</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -13477,13 +13477,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.81786258915147003</v>
+        <v>0.81807064960546005</v>
       </c>
       <c r="C8">
         <v>7</v>
       </c>
       <c r="D8">
-        <v>0.80030632985618799</v>
+        <v>0.80688383600059899</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -13491,13 +13491,13 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.82412997501646701</v>
+        <v>0.824403345933584</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
       <c r="D9">
-        <v>0.81809960410622795</v>
+        <v>0.78976111820765604</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -13505,13 +13505,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.83309965084534299</v>
+        <v>0.83336065872968401</v>
       </c>
       <c r="C10">
         <v>9</v>
       </c>
       <c r="D10">
-        <v>0.81544775870104802</v>
+        <v>0.774079805845171</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -13519,13 +13519,13 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.84630228569939203</v>
+        <v>0.84652181328391796</v>
       </c>
       <c r="C11">
         <v>10</v>
       </c>
       <c r="D11">
-        <v>0.80563780700709098</v>
+        <v>0.730582759530225</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -13533,13 +13533,13 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.81934712199704096</v>
+        <v>0.81964353153660996</v>
       </c>
       <c r="C12">
         <v>11</v>
       </c>
       <c r="D12">
-        <v>0.77834476945300302</v>
+        <v>0.67512694541234297</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -13547,13 +13547,13 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.79627680291540504</v>
+        <v>0.79662606808636205</v>
       </c>
       <c r="C13">
         <v>12</v>
       </c>
       <c r="D13">
-        <v>0.726435315594398</v>
+        <v>0.61874202576439097</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -13561,13 +13561,13 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.75603794320373396</v>
+        <v>0.75639660763948102</v>
       </c>
       <c r="C14">
         <v>13</v>
       </c>
       <c r="D14">
-        <v>0.71281340240402002</v>
+        <v>0.56050129904967905</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -13575,13 +13575,13 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.72587809206409604</v>
+        <v>0.72622632080295801</v>
       </c>
       <c r="C15">
         <v>14</v>
       </c>
       <c r="D15">
-        <v>0.67850844524521703</v>
+        <v>0.53640921922487095</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -13589,13 +13589,13 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.69049950945625904</v>
+        <v>0.69088788029685499</v>
       </c>
       <c r="C16">
         <v>15</v>
       </c>
       <c r="D16">
-        <v>0.63408843291719097</v>
+        <v>0.51703931902566302</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -13603,13 +13603,13 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.65978415609247898</v>
+        <v>0.66019943349735799</v>
       </c>
       <c r="C17">
         <v>16</v>
       </c>
       <c r="D17">
-        <v>0.58803624309374802</v>
+        <v>0.500245711080616</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -13617,13 +13617,13 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.614684031765098</v>
+        <v>0.61507992033238601</v>
       </c>
       <c r="C18">
         <v>17</v>
       </c>
       <c r="D18">
-        <v>0.55718182818927098</v>
+        <v>0.484643383715056</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -13631,13 +13631,13 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.60175523923192697</v>
+        <v>0.60210579766070005</v>
       </c>
       <c r="C19">
         <v>18</v>
       </c>
       <c r="D19">
-        <v>0.53615822511116396</v>
+        <v>0.46791157784166798</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -13645,13 +13645,13 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.57404522530574398</v>
+        <v>0.57446704068642596</v>
       </c>
       <c r="C20">
         <v>19</v>
       </c>
       <c r="D20">
-        <v>0.53313269679365705</v>
+        <v>0.47592419269982</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -13659,13 +13659,13 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.559672838670213</v>
+        <v>0.56011853004919498</v>
       </c>
       <c r="C21">
         <v>20</v>
       </c>
       <c r="D21">
-        <v>0.50687074119832498</v>
+        <v>0.45627693797462998</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -13673,13 +13673,13 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0.53736228271698605</v>
+        <v>0.53781197847073303</v>
       </c>
       <c r="C22">
         <v>21</v>
       </c>
       <c r="D22">
-        <v>0.49867072951340302</v>
+        <v>0.45921434713395298</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -13687,13 +13687,13 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.52606070980841402</v>
+        <v>0.52649596192260395</v>
       </c>
       <c r="C23">
         <v>22</v>
       </c>
       <c r="D23">
-        <v>0.49320149064164898</v>
+        <v>0.45575766435808401</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -13701,13 +13701,13 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>0.49839057703582801</v>
+        <v>0.49884128563318197</v>
       </c>
       <c r="C24">
         <v>23</v>
       </c>
       <c r="D24">
-        <v>0.473647399762957</v>
+        <v>0.44347750227716098</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -13715,13 +13715,13 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0.49674980397642499</v>
+        <v>0.49719740709377303</v>
       </c>
       <c r="C25">
         <v>24</v>
       </c>
       <c r="D25">
-        <v>0.45038720937019899</v>
+        <v>0.42496433140641499</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -13729,13 +13729,13 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>0.49302189206452601</v>
+        <v>0.49348048858460197</v>
       </c>
       <c r="C26">
         <v>25</v>
       </c>
       <c r="D26">
-        <v>0.45082879836748602</v>
+        <v>0.433224168039338</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -13743,13 +13743,13 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>0.49056595631507799</v>
+        <v>0.49100768337885198</v>
       </c>
       <c r="C27">
         <v>26</v>
       </c>
       <c r="D27">
-        <v>0.43486008618920202</v>
+        <v>0.446257153365613</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -13757,13 +13757,13 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>0.47642252149867398</v>
+        <v>0.47685951082876299</v>
       </c>
       <c r="C28">
         <v>27</v>
       </c>
       <c r="D28">
-        <v>0.433947046222808</v>
+        <v>0.44166406434991601</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -13771,13 +13771,13 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>0.47969611189959699</v>
+        <v>0.480107240085551</v>
       </c>
       <c r="C29">
         <v>28</v>
       </c>
       <c r="D29">
-        <v>0.42518474214597402</v>
+        <v>0.438585237253306</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -13785,13 +13785,13 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>0.47278711190129602</v>
+        <v>0.47319353462423303</v>
       </c>
       <c r="C30">
         <v>29</v>
       </c>
       <c r="D30">
-        <v>0.42733963280660903</v>
+        <v>0.43296303442863099</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -13799,13 +13799,13 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.461229445176496</v>
+        <v>0.46170513841057698</v>
       </c>
       <c r="C31">
         <v>30</v>
       </c>
       <c r="D31">
-        <v>0.41810427574568199</v>
+        <v>0.45270000392256599</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -13813,13 +13813,13 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>0.46392120477802001</v>
+        <v>0.464350482353028</v>
       </c>
       <c r="C32">
         <v>31</v>
       </c>
       <c r="D32">
-        <v>0.436609156212585</v>
+        <v>0.45960422821835101</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -13827,13 +13827,13 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.45530688919616502</v>
+        <v>0.45572799216972898</v>
       </c>
       <c r="C33">
         <v>32</v>
       </c>
       <c r="D33">
-        <v>0.43651855719183602</v>
+        <v>0.44448562327177699</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -13841,13 +13841,13 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>0.44504607446079097</v>
+        <v>0.44545517737214102</v>
       </c>
       <c r="C34">
         <v>33</v>
       </c>
       <c r="D34">
-        <v>0.436463127747659</v>
+        <v>0.43245412942459899</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -13855,13 +13855,13 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>0.44116830619323999</v>
+        <v>0.44152762477581903</v>
       </c>
       <c r="C35">
         <v>34</v>
       </c>
       <c r="D35">
-        <v>0.42919533274959998</v>
+        <v>0.44449669170394501</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -13869,13 +13869,13 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>0.45663593545159198</v>
+        <v>0.45699015000113002</v>
       </c>
       <c r="C36">
         <v>35</v>
       </c>
       <c r="D36">
-        <v>0.43498570366974698</v>
+        <v>0.43725398447184899</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -13883,13 +13883,13 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0.44270502297917702</v>
+        <v>0.44306527457008599</v>
       </c>
       <c r="C37">
         <v>36</v>
       </c>
       <c r="D37">
-        <v>0.423854802030671</v>
+        <v>0.42639494007614398</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -13897,13 +13897,13 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>0.44338868934126002</v>
+        <v>0.44379483308733902</v>
       </c>
       <c r="C38">
         <v>37</v>
       </c>
       <c r="D38">
-        <v>0.41374048080776898</v>
+        <v>0.42637078851808502</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -13911,13 +13911,13 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>0.43121230545956202</v>
+        <v>0.43162842811778701</v>
       </c>
       <c r="C39">
         <v>38</v>
       </c>
       <c r="D39">
-        <v>0.419172535140034</v>
+        <v>0.45067180975557303</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -13925,13 +13925,13 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>0.436219893068164</v>
+        <v>0.43664144398022497</v>
       </c>
       <c r="C40">
         <v>39</v>
       </c>
       <c r="D40">
-        <v>0.417197497891661</v>
+        <v>0.43494374478353498</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -13939,13 +13939,13 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>0.43428562870499199</v>
+        <v>0.434722198627564</v>
       </c>
       <c r="C41">
         <v>40</v>
       </c>
       <c r="D41">
-        <v>0.42286756274987403</v>
+        <v>0.42750802187060599</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -13953,13 +13953,13 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>0.43514931399264301</v>
+        <v>0.435601053644738</v>
       </c>
       <c r="C42">
         <v>41</v>
       </c>
       <c r="D42">
-        <v>0.43086344738056398</v>
+        <v>0.433094664618769</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -13967,13 +13967,13 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>0.442056120019932</v>
+        <v>0.44248234587130503</v>
       </c>
       <c r="C43">
         <v>42</v>
       </c>
       <c r="D43">
-        <v>0.42490235137765803</v>
+        <v>0.42593593971446703</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -13981,13 +13981,13 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>0.43322661058707701</v>
+        <v>0.43366561847336699</v>
       </c>
       <c r="C44">
         <v>43</v>
       </c>
       <c r="D44">
-        <v>0.43602749389336498</v>
+        <v>0.42209466948455898</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -13995,13 +13995,13 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>0.43138005773309701</v>
+        <v>0.43179942584511</v>
       </c>
       <c r="C45">
         <v>44</v>
       </c>
       <c r="D45">
-        <v>0.43179844839018799</v>
+        <v>0.43599641679122503</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -14009,13 +14009,13 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>0.43438401107605001</v>
+        <v>0.43481588718970998</v>
       </c>
       <c r="C46">
         <v>45</v>
       </c>
       <c r="D46">
-        <v>0.42829952941053501</v>
+        <v>0.43220452521299002</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -14023,13 +14023,13 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>0.43825126033443701</v>
+        <v>0.43870323887586998</v>
       </c>
       <c r="C47">
         <v>46</v>
       </c>
       <c r="D47">
-        <v>0.41867300035092297</v>
+        <v>0.43313261793802199</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -14037,13 +14037,13 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>0.449400976562289</v>
+        <v>0.44983228002756298</v>
       </c>
       <c r="C48">
         <v>47</v>
       </c>
       <c r="D48">
-        <v>0.44348014084576298</v>
+        <v>0.427436882528828</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -14051,13 +14051,13 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>0.44744150935195398</v>
+        <v>0.4478985976582</v>
       </c>
       <c r="C49">
         <v>48</v>
       </c>
       <c r="D49">
-        <v>0.44637596730389001</v>
+        <v>0.433993100223518</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -14065,13 +14065,13 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>0.45340426252174398</v>
+        <v>0.45383955760938799</v>
       </c>
       <c r="C50">
         <v>49</v>
       </c>
       <c r="D50">
-        <v>0.42827045781535</v>
+        <v>0.43868890221316398</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -14079,13 +14079,13 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>0.47172911767634601</v>
+        <v>0.47215523970996898</v>
       </c>
       <c r="C51">
         <v>50</v>
       </c>
       <c r="D51">
-        <v>0.441772369366146</v>
+        <v>0.43132629596622901</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -14093,13 +14093,13 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>0.46483759642641298</v>
+        <v>0.46527833834614202</v>
       </c>
       <c r="C52">
         <v>51</v>
       </c>
       <c r="D52">
-        <v>0.430533553846915</v>
+        <v>0.43977625690838401</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -14107,13 +14107,13 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>0.44658852808927602</v>
+        <v>0.447043945111954</v>
       </c>
       <c r="C53">
         <v>52</v>
       </c>
       <c r="D53">
-        <v>0.42570471559617501</v>
+        <v>0.43503031676729098</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -14121,13 +14121,13 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>0.423152864070791</v>
+        <v>0.42366191650947399</v>
       </c>
       <c r="C54">
         <v>53</v>
       </c>
       <c r="D54">
-        <v>0.40993580891717701</v>
+        <v>0.41925587004107301</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -14135,13 +14135,13 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>0.41541129337730798</v>
+        <v>0.41593347807768799</v>
       </c>
       <c r="C55">
         <v>54</v>
       </c>
       <c r="D55">
-        <v>0.41443535009536597</v>
+        <v>0.41439062357508799</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -14149,13 +14149,13 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>0.42413575012392601</v>
+        <v>0.42470349988948097</v>
       </c>
       <c r="C56">
         <v>55</v>
       </c>
       <c r="D56">
-        <v>0.44405364220156901</v>
+        <v>0.41821733749786</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -14163,13 +14163,13 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>0.42343393647435501</v>
+        <v>0.42399948738135801</v>
       </c>
       <c r="C57">
         <v>56</v>
       </c>
       <c r="D57">
-        <v>0.42905659708647198</v>
+        <v>0.432874380402967</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -14177,13 +14177,13 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>0.43992861489573198</v>
+        <v>0.44044625494893203</v>
       </c>
       <c r="C58">
         <v>57</v>
       </c>
       <c r="D58">
-        <v>0.40745946475342598</v>
+        <v>0.41124166178965998</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -14191,13 +14191,13 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>0.44746590871184799</v>
+        <v>0.44796517200416702</v>
       </c>
       <c r="C59">
         <v>58</v>
       </c>
       <c r="D59">
-        <v>0.41577650028864299</v>
+        <v>0.41441029043151201</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -14205,13 +14205,13 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>0.43005095565944301</v>
+        <v>0.43060952007012399</v>
       </c>
       <c r="C60">
         <v>59</v>
       </c>
       <c r="D60">
-        <v>0.413374471993948</v>
+        <v>0.42458987376603802</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -14219,13 +14219,13 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>0.42694431354073897</v>
+        <v>0.42748019738957599</v>
       </c>
       <c r="C61">
         <v>60</v>
       </c>
       <c r="D61">
-        <v>0.40597795616978799</v>
+        <v>0.434830710163643</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -14233,13 +14233,13 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>0.43844910447376401</v>
+        <v>0.43898692697111003</v>
       </c>
       <c r="C62">
         <v>61</v>
       </c>
       <c r="D62">
-        <v>0.40695264531613801</v>
+        <v>0.442058648947251</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -14247,13 +14247,13 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>0.41960948354176902</v>
+        <v>0.42017298195222402</v>
       </c>
       <c r="C63">
         <v>62</v>
       </c>
       <c r="D63">
-        <v>0.42628385854080703</v>
+        <v>0.41953899809209799</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -14261,13 +14261,13 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>0.43988316818477402</v>
+        <v>0.44038777393823397</v>
       </c>
       <c r="C64">
         <v>63</v>
       </c>
       <c r="D64">
-        <v>0.414625101227799</v>
+        <v>0.41532718042779199</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -14275,13 +14275,13 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>0.44847176966455099</v>
+        <v>0.448908825196151</v>
       </c>
       <c r="C65">
         <v>64</v>
       </c>
       <c r="D65">
-        <v>0.41606518548181398</v>
+        <v>0.42907932117533698</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -14289,13 +14289,13 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>0.45234610874147402</v>
+        <v>0.45286047931475798</v>
       </c>
       <c r="C66">
         <v>65</v>
       </c>
       <c r="D66">
-        <v>0.40948921822852802</v>
+        <v>0.43001316148949098</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -14303,13 +14303,13 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>0.438113785044422</v>
+        <v>0.43861672505837601</v>
       </c>
       <c r="C67">
         <v>66</v>
       </c>
       <c r="D67">
-        <v>0.41464277163319901</v>
+        <v>0.44113709240117599</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -14317,13 +14317,13 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>0.44462901163156299</v>
+        <v>0.44511319199681099</v>
       </c>
       <c r="C68">
         <v>67</v>
       </c>
       <c r="D68">
-        <v>0.42351543952509602</v>
+        <v>0.43980577711858498</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -14331,13 +14331,13 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>0.44136244756225601</v>
+        <v>0.44185253035361</v>
       </c>
       <c r="C69">
         <v>68</v>
       </c>
       <c r="D69">
-        <v>0.42800885054617199</v>
+        <v>0.43948930173637002</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -14345,13 +14345,13 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>0.43513166612583698</v>
+        <v>0.435651257977615</v>
       </c>
       <c r="C70">
         <v>69</v>
       </c>
       <c r="D70">
-        <v>0.42683558779909198</v>
+        <v>0.44706616000657301</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -14359,13 +14359,13 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>0.43934148832626801</v>
+        <v>0.43988995023731098</v>
       </c>
       <c r="C71">
         <v>70</v>
       </c>
       <c r="D71">
-        <v>0.42118228405132702</v>
+        <v>0.42858392088623698</v>
       </c>
     </row>
   </sheetData>

--- a/InitializationResults/WithTrack/Comparison of NSGAII with NSGAII_SI for each generation (on average).xlsx
+++ b/InitializationResults/WithTrack/Comparison of NSGAII with NSGAII_SI for each generation (on average).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="10995" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="10995"/>
   </bookViews>
   <sheets>
     <sheet name="EPS" sheetId="1" r:id="rId1"/>
@@ -897,11 +897,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="346524912"/>
-        <c:axId val="346532360"/>
+        <c:axId val="356932088"/>
+        <c:axId val="356929344"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="346524912"/>
+        <c:axId val="356932088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1014,12 +1014,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346532360"/>
+        <c:crossAx val="356929344"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="346532360"/>
+        <c:axId val="356929344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1076,7 +1076,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346524912"/>
+        <c:crossAx val="356932088"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1962,11 +1962,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="346527656"/>
-        <c:axId val="346525304"/>
+        <c:axId val="356932480"/>
+        <c:axId val="356930128"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="346527656"/>
+        <c:axId val="356932480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2079,12 +2079,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346525304"/>
+        <c:crossAx val="356930128"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="346525304"/>
+        <c:axId val="356930128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2141,7 +2141,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346527656"/>
+        <c:crossAx val="356932480"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3027,11 +3027,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="346530792"/>
-        <c:axId val="346523736"/>
+        <c:axId val="356930912"/>
+        <c:axId val="360335112"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="346530792"/>
+        <c:axId val="356930912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3144,12 +3144,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346523736"/>
+        <c:crossAx val="360335112"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="346523736"/>
+        <c:axId val="360335112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0.65000000000000013"/>
@@ -3207,7 +3207,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346530792"/>
+        <c:crossAx val="356930912"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4093,11 +4093,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="346531576"/>
-        <c:axId val="346525696"/>
+        <c:axId val="360337464"/>
+        <c:axId val="360338248"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="346531576"/>
+        <c:axId val="360337464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4210,12 +4210,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346525696"/>
+        <c:crossAx val="360338248"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="346525696"/>
+        <c:axId val="360338248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4272,7 +4272,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346531576"/>
+        <c:crossAx val="360337464"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5158,11 +5158,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="346522560"/>
-        <c:axId val="346526872"/>
+        <c:axId val="360335504"/>
+        <c:axId val="360337856"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="346522560"/>
+        <c:axId val="360335504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5275,12 +5275,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346526872"/>
+        <c:crossAx val="360337856"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="346526872"/>
+        <c:axId val="360337856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5337,7 +5337,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346522560"/>
+        <c:crossAx val="360335504"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
